--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,413 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>465200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>469400</v>
+      </c>
+      <c r="F8" s="3">
         <v>448700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>423300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>399800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>429300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>370500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>354000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>307100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>349100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>285700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>296600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>287200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>345000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>268300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>258000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>369300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>444600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>364800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>372400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>343600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>445000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>362500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>379200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>351900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>387000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>348500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>349700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>340600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>284900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>282300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>281500</v>
+      </c>
+      <c r="F9" s="3">
         <v>280100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>259700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>249900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>267100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>237400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>229400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>203100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>217300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>189900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>194300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>182800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>219200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>176600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>169700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>255200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>301100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>258600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>264200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>260400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>309800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>274800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>281500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>261800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>306100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>263400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>273600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>252500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>177700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>187900</v>
+      </c>
+      <c r="F10" s="3">
         <v>168600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>163600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>149900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>162200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>133100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>124600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>104000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>131800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>95800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>102300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>104400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>125800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>91700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>88300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>114100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>143500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>106200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>108200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>83200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>135200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>87700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>97700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>90100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>80900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>85100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>76100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>88100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>107200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,8 +1120,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1214,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,174 +1312,186 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>13700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>24200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
-      </c>
-      <c r="P14" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1000</v>
       </c>
       <c r="R14" s="3">
         <v>300</v>
       </c>
       <c r="S14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T14" s="3">
+        <v>300</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>2000</v>
       </c>
       <c r="AA14" s="3">
         <v>1600</v>
       </c>
       <c r="AB14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-9200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>27600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>14600</v>
+        <v>14800</v>
       </c>
       <c r="E15" s="3">
         <v>11500</v>
       </c>
       <c r="F15" s="3">
+        <v>14600</v>
+      </c>
+      <c r="G15" s="3">
+        <v>11500</v>
+      </c>
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>5400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>6700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>9300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>5600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>5500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>6500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>4000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>5700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>2600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>2900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>2000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>1600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>1500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>1700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>800</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>100</v>
       </c>
       <c r="AB15" s="3">
         <v>200</v>
@@ -1458,13 +1503,19 @@
         <v>200</v>
       </c>
       <c r="AE15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1545,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>400600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>406300</v>
+      </c>
+      <c r="F17" s="3">
         <v>391000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>372000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>350000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>454200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>334300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>326800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>295700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>320100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>268000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>279500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>262200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>302100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>247900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>240500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>336600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>394200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>337200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>346100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>340600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>393200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>349100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>356500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>332600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>386200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>317300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>345600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>322800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>267000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>63100</v>
+      </c>
+      <c r="F18" s="3">
         <v>57700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>51300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>49800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-24900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>36200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>27200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>29000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>17700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>17100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>25000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>42900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>20400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>17500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>32700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>50400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>27600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>26300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>51800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>13400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>22700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>19300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>31200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>17800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>17900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,468 +1777,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-23600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>6600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-8100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>6400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>7500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-8600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-14500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>7500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-11100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>67700</v>
+      </c>
+      <c r="F21" s="3">
         <v>78000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>67500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>63500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-10500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>23900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>37400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>32000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>31100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>33600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>32500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>43600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>47400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>33300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>32300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>42600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>45700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>37100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>37300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>18600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>48600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>22300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>32000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>27400</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>8600</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>37400</v>
       </c>
       <c r="AC21" s="3">
         <v>8600</v>
       </c>
       <c r="AD21" s="3">
+        <v>37400</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AF21" s="3">
         <v>23800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>21100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F22" s="3">
         <v>10200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>2400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>2200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>4200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>4400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>4500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>4800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>4700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>5400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>5000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>5300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>5300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>6200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>5900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>5100</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>4300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4200</v>
       </c>
       <c r="AB22" s="3">
         <v>4300</v>
       </c>
       <c r="AC22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>4600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>4000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>3700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>41700</v>
+      </c>
+      <c r="F23" s="3">
         <v>48100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>46100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>50400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-22000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>10000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>23500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>15600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>18700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>18100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>20100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>28300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>29900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>18700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>18200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>28700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>30500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>24000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>23500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>34500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>8500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>20100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>16500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>26800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>13500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>12600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F24" s="3">
         <v>12400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>11300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>2800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-2500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>2600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>4100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>4600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-4600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>4800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>6000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>3000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2361,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F26" s="3">
         <v>35700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>38300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>39100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-24800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>12500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>19100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>13000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>17600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>13900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>17700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>23000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>33500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>15200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>22700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>28500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>21200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>19400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>39100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>7300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>18600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>13900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>71800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>22000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>10300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>9600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>49200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>31600</v>
+      </c>
+      <c r="F27" s="3">
         <v>35700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>38300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>39100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-24800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>12500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>19100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>13000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>17600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>13900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>17700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>23000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>33500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>15600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>15200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>22700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>34100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>21200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>19400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>39100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>7300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>18600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>13900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>71800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>22000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>10300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>9600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,100 +2655,112 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="3">
         <v>-56100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-2300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>3700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-2500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-9400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-6100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-1600</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-11600</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>316400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>91000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>11600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-7100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>7200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>11900</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-3100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-1400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>4400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-700</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>7100</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2851,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,192 +2949,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>23600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-6600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>8100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-6400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-7500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>8600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>14500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-7500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>11100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-20400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>36000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>42800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-27300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>13000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>11400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>330300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>108700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>34600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>26400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>22800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>27100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>22700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>31000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>21500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>19200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>39200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>6600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>23000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>12400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>58600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>22300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>17400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3243,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-20400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>36000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>42800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-27300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>13000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>11400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>330300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>108700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>34600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>26400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>22800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>27100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>22700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>31000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>21500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>19200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>39200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>6600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>23000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>12400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>58600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>22300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>17400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3484,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,100 +3520,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>99400</v>
+      </c>
+      <c r="F41" s="3">
         <v>100900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>87100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>204800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>147800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>183400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>189800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>262800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>388200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>560100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>69100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>106900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>64000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>70700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>190200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>163100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>54700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>49300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>34600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>39000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>68800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>61900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>66700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>103700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>124300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>87200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>83500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>92700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>99600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3533,376 +3712,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>349600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>296400</v>
+      </c>
+      <c r="F43" s="3">
         <v>338100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>318000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>307100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>294300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>296300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>274400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>253400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>261000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>238400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>267600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>342700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>270600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>327200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>329900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>335900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>352300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>333300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>332100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>338100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>360300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>346400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>339500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>313000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>267500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>266600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>252000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>232700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>251700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>295100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>276700</v>
+      </c>
+      <c r="F44" s="3">
         <v>291500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>299600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>265700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>244000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>265200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>235800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>220700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>189800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>170300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>157700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>169700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>143100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>179300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>181600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>175100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>154900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>157700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>155500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>151500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>128800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>143500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>141900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>109300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>143000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>165600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>168300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>159200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>145700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F45" s="3">
         <v>38100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>34300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>42200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>35000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>92800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>78600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>78600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>64400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>77700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>407000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>76200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>185500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>71400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>67300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>69900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>70200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>22800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>23300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>25100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>40500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>71300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>74300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>72500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>97700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>39600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>35100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>26500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>30600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>779600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>709600</v>
+      </c>
+      <c r="F46" s="3">
         <v>768600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>739000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>819800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>721100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>837700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>778600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>815500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>903400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1046500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>901400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>695500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>675100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>648600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>769000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>744000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>632100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>563100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>545500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>553700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>598400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>623100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>622400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>598500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>632500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>559000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>538900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>511100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>527600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3993,192 +4202,210 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>140500</v>
+      </c>
+      <c r="F48" s="3">
         <v>135100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>134700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>110300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>156200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>107000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>109600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>110700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>155000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>108000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>113000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>186600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>147300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>187600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>178100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>176900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>209800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>202000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>199900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>204600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>184200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>185000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>188200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>185800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>186600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>188800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>191600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>193600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>195500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1605100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1385600</v>
+      </c>
+      <c r="F49" s="3">
         <v>1362800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1385500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>854200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>856900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>852300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>875800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>896500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>872800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>741200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>735000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>800500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>673600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>792800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>697500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>694200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>701000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>660300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>660600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>661900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>592800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>594100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>595200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>478100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>463500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>463100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>462500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>459900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>458300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4496,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,100 +4594,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>197700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>204000</v>
+      </c>
+      <c r="F52" s="3">
         <v>206500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>242400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>237100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>196700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>685500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>725600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>744500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>697400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>594100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>661100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>614400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1447500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>621000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>611800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>606800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>591600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>637000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>661300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>681200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>682100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>704200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>718000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>749700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>757800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>721900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>736400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>733800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>731100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,100 +4790,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2799600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2439700</v>
+      </c>
+      <c r="F54" s="3">
         <v>2473000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2501600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2021400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1930900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2482500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2489600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2567200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2628600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2489800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2410500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2297000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2333700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2250000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2256400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2221900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2134500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2062400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2067300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2101400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2057500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2106400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2123800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4928,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,560 +4964,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>151400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>118700</v>
+      </c>
+      <c r="F57" s="3">
         <v>131700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>131000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>120000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>124500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>125200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>116200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>111000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>119600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>112300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>86800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>135000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>102100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>134500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>137900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>148000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>141600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>132500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>135900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>142200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>153600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>141200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>150700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>145000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>159700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>143300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>140800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>133100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>137600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>337800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>35200</v>
+      </c>
+      <c r="F58" s="3">
         <v>144100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>142500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>72400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>3800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>15100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>15200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>13700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>178700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>108900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>121800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>113600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>270900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>262900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>143600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>59100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>73600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>89200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>49900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>122400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>133300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>11700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>7500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>57000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>52000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>35100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>32700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>205600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>247300</v>
+      </c>
+      <c r="F59" s="3">
         <v>217900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>216100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>201500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>205500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>246900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>236900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>267900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>304700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>351500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>442100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>342900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>361600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>314100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>295200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>291200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>323400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>275200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>257100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>263600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>266700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>263400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>259900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>271500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>293800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>285700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>292500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>282700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>306000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>694800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>401200</v>
+      </c>
+      <c r="F60" s="3">
         <v>493700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>489600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>393900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>333800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>374400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>368200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>393900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>439500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>477500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>707600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>586800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>572100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>562200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>704000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>702100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>608600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>466800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>466600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>495000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>470200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>527000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>543900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>428200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>461000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>486000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>485300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>450900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>476300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>516600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>523100</v>
+      </c>
+      <c r="F61" s="3">
         <v>529800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>533100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>241500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>243000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>244600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>224500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>227700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>230800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>233900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>238000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>282600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>304000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>350300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>247000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>248600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>249900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>323800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>328000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>332300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>331900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>340600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>340600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>344900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>349300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>311000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>315400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>319400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>323500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>350700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>320800</v>
+      </c>
+      <c r="F62" s="3">
         <v>302600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>306300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>259900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>274900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>783800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>808300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>829800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>855400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>718100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>736700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>766800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>817500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>754400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>753300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>756100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>773600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>810500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>836000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>858800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>840500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>869100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>880700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>905800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>915400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>880800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>920000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>917100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>921100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5646,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5744,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,100 +5842,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1562100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1245100</v>
+      </c>
+      <c r="F66" s="3">
         <v>1326100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1329000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>895300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>851700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1402800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1401000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1451400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1525700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1429500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1682300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1636200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1693600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1666900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1704300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1706800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1632100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1601100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1630600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1686100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1642600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1736700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1765200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5980,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +6074,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6172,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6270,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,100 +6368,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>38300</v>
+      </c>
+      <c r="F72" s="3">
         <v>6800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>27200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-8800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-51600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-24300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-40400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-51800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-68700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-399800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-461300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-477200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-512700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-535500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-562600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-584800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-610200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-631700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-650900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-650100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-701300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-707900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6564,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6662,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,100 +6760,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1237500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1194600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1146900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1172600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1126100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1079200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1079700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1088600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1115800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1102900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1060300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>728200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>660800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>640100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>583100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>552100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>515100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>502400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>461300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>436700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>415300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>414900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>369700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>358600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>333200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>314700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>255000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>208700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>211000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>191600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6956,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>31500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-20400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>36000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>42800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-27300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>13000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>11400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>330300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>108700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>34600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>26400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>22800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>27100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>22700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>31000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>21500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>19200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>39200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>6600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>23000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>12400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>58600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>22300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>17400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,85 +7197,87 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F83" s="3">
         <v>19700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>16000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>10700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>9500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>11600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>14000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>10200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>12000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>9000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>11100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>13100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>10100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>9300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>9200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>9800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>8100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>8500</v>
       </c>
       <c r="V83" s="3">
         <v>8100</v>
       </c>
       <c r="W83" s="3">
+        <v>8500</v>
+      </c>
+      <c r="X83" s="3">
+        <v>8100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>7900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>7900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>6800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>6300</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>6300</v>
       </c>
       <c r="AC83" s="3">
         <v>6300</v>
@@ -6889,13 +7286,19 @@
         <v>6300</v>
       </c>
       <c r="AE83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>4800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7389,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7487,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7585,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7683,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7781,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>126500</v>
+      </c>
+      <c r="F89" s="3">
         <v>14400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>72000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-26300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-14000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-39300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-57200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>20800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>74900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>18700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>60200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>69900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>30100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>26700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>78800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>43300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>15900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>10600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>97300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>8600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>2400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>2300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>56100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>6900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>52100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7919,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-4700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-5900</v>
       </c>
       <c r="H91" s="3">
         <v>-4000</v>
       </c>
       <c r="I91" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-7100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-2500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-3700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-4400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-3600</v>
       </c>
       <c r="AC91" s="3">
         <v>-2600</v>
       </c>
       <c r="AD91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +8111,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +8209,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-303900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-6400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-550900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-6800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-57800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-184500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>582000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-84300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-24300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-93500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-5800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-67000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-11200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-74700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8347,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7974,8 +8441,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8539,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8637,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,280 +8735,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-115500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>363300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>62900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>6200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-35000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-11400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-167700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>26500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-25600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-48600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>6800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>113000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-6400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-18400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-19000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>32700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-86000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>117500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>1200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>12900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
+        <v>900</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>3100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-1700</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>0</v>
       </c>
       <c r="AA101" s="3">
         <v>-900</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>3600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F102" s="3">
         <v>6400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-117100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>55600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-30200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-74300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-126500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-164100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>491000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-37800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>38600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-2400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-119500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>27100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>108400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>5400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>14700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-4400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-29800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>6900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-37000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>37100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>3700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>16200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,438 +656,451 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>501300</v>
+      </c>
+      <c r="E8" s="3">
         <v>465200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>469400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>448700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>423300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>399800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>429300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>370500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>354000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>307100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>349100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>285700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>296600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>287200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>345000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>268300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>258000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>369300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>444600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>364800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>372400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>343600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>445000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>362500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>379200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>351900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>387000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>348500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>349700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>340600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>284900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>300500</v>
+      </c>
+      <c r="E9" s="3">
         <v>282300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>281500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>280100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>259700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>249900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>267100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>237400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>229400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>203100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>217300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>189900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>194300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>182800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>219200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>176600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>169700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>255200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>301100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>258600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>264200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>260400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>309800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>274800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>281500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>261800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>306100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>263400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>273600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>252500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>177700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200800</v>
+      </c>
+      <c r="E10" s="3">
         <v>182900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>187900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>168600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>163600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>149900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>162200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>133100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>124600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>104000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>131800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>95800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>102300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>104400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>125800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>91700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>88300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>114100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>143500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>106200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>108200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>83200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>135200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>87700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>97700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>90100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>80900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>85100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>76100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>88100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>107200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1135,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1234,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,204 +1335,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>500</v>
       </c>
       <c r="AF14" s="3">
         <v>500</v>
       </c>
       <c r="AG14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH14" s="3">
         <v>27600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E15" s="3">
         <v>14800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>1600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>100</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>200</v>
       </c>
       <c r="AG15" s="3">
         <v>200</v>
       </c>
       <c r="AH15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1547,204 +1573,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>426700</v>
+      </c>
+      <c r="E17" s="3">
         <v>400600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>406300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>391000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>372000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>350000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>454200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>334300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>326800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>295700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>320100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>268000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>279500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>262200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>302100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>247900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>240500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>336600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>394200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>337200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>346100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>340600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>393200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>349100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>356500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>332600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>386200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>317300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>345600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>322800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>267000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E18" s="3">
         <v>64600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>51300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>49800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-24900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>36200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>29000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>42900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>32700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>50400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>27600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>26300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>51800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>22700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>19300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>31200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1779,498 +1812,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>1500</v>
       </c>
       <c r="AC20" s="3">
         <v>1500</v>
       </c>
       <c r="AD20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E21" s="3">
         <v>81900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>67700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>78000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>67500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>63500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-10500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>37400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>43600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>33300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>42600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>37100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>37300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>18600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>48600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>32000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>8600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>37400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>23800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>21100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E22" s="3">
         <v>9800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>5300</v>
       </c>
       <c r="X22" s="3">
         <v>5300</v>
       </c>
       <c r="Y22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>6200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E23" s="3">
         <v>51100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>41700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-22000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>28300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>29900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>23500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>34500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>20100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>16500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>13500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2367,204 +2416,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E26" s="3">
         <v>49200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>38300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>39100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-24800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>12500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>22700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>28500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>21200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>39100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>18600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>13900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>71800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>22000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E27" s="3">
         <v>49200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>35700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>38300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>39100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>12500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>22700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>34100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>21200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>71800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>22000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2661,106 +2719,112 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-200</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-56100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-2300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>3700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-9400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-1600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-11600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>316400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>91000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>11600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-7100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>7200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>11900</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-3100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>4400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>300</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>7100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2857,8 +2921,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2955,204 +3022,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AC32" s="3">
         <v>-1500</v>
       </c>
       <c r="AD32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E33" s="3">
         <v>49000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-20400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>36000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>42800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>330300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>108700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>34600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>26400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>22800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>27100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>22700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>31000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>19200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>23000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>58600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3249,209 +3325,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E35" s="3">
         <v>49000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-20400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>36000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>42800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>330300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>108700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>34600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>26400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>22800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>27100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>31000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>19200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>23000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>58600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3486,8 +3571,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3522,106 +3608,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E41" s="3">
         <v>100500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>99400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>204800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>147800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>183400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>189800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>262800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>388200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>560100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>69100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>106900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>64000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>70700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>190200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>163100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>34600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>61900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>66700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>103700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>124300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>87200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>83500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>92700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>99600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3718,400 +3808,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>357900</v>
+      </c>
+      <c r="E43" s="3">
         <v>349600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>296400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>338100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>318000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>307100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>294300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>296300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>274400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>253400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>261000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>238400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>267600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>342700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>270600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>327200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>329900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>335900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>352300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>333300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>332100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>338100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>360300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>346400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>339500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>313000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>267500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>266600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>252000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>232700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>251700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>292700</v>
+      </c>
+      <c r="E44" s="3">
         <v>295100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>276700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>291500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>299600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>265700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>244000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>265200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>235800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>220700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>189800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>170300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>157700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>169700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>143100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>179300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>181600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>175100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>154900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>157700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>155500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>151500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>128800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>143500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>141900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>109300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>143000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>165600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>168300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>159200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>145700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E45" s="3">
         <v>34400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>34300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>35000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>92800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>78600</v>
       </c>
       <c r="L45" s="3">
         <v>78600</v>
       </c>
       <c r="M45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="N45" s="3">
         <v>64400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>77700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>407000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>76200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>185500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>69900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>71300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>74300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>72500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>97700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>39600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>35100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>26500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>30600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>808700</v>
+      </c>
+      <c r="E46" s="3">
         <v>779600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>709600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>768600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>739000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>819800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>721100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>837700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>778600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>815500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>903400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1046500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>901400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>695500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>675100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>648600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>769000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>744000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>632100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>563100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>545500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>553700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>598400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>623100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>622400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>598500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>632500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>559000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>538900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>511100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>527600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4208,204 +4313,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>270900</v>
+      </c>
+      <c r="E48" s="3">
         <v>217200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>140500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>135100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>134700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>110300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>156200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>107000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>109600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>110700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>155000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>108000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>113000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>186600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>147300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>187600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>178100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>176900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>209800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>202000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>199900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>204600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>184200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>185000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>188200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>185800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>186600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>188800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>191600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>193600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>195500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1587700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1605100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1385600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1362800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1385500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>854200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>856900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>852300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>875800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>896500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>872800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>741200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>735000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>800500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>673600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>792800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>697500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>694200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>701000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>660300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>660600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>661900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>592800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>594100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>595200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>478100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>463500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>463100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>462500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>459900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>458300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4502,8 +4616,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4600,106 +4717,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>115800</v>
+      </c>
+      <c r="E52" s="3">
         <v>197700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>204000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>206500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>242400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>237100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>196700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>685500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>725600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>744500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>697400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>594100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>661100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>614400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1447500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>621000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>611800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>606800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>591600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>637000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>661300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>681200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>682100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>704200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>718000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>749700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>757800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>721900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>736400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>733800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>731100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4796,106 +4919,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2783100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2799600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2439700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2473000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2501600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2021400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1930900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2482500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2489600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2567200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2628600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2489800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2410500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2297000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2333700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2250000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2256400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2221900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2134500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2062400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2067300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2101400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2057500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4930,8 +5059,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4966,596 +5096,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E57" s="3">
         <v>151400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>118700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>131700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>131000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>124500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>125200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>116200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>111000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>119600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>112300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>86800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>135000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>102100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>134500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>137900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>148000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>141600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>132500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>135900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>142200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>153600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>141200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>150700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>145000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>159700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>143300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>140800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>133100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>137600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E58" s="3">
         <v>337800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>35200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>144100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>142500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>72400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>178700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>108900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>121800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>113600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>270900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>262900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>143600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>59100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>73600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>89200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>49900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>122400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>133300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>57000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>52000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>35100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>32700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E59" s="3">
         <v>205600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>247300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>217900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>216100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>201500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>205500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>246900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>236900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>267900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>304700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>351500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>442100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>342900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>361600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>314100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>295200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>291200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>323400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>275200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>257100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>263600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>266700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>263400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>259900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>271500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>293800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>285700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>292500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>282700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>306000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>633300</v>
+      </c>
+      <c r="E60" s="3">
         <v>694800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>401200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>493700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>489600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>393900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>333800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>374400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>368200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>393900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>439500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>477500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>707600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>586800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>572100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>562200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>704000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>702100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>608600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>466800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>466600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>495000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>470200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>527000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>543900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>428200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>461000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>486000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>485300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>450900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>476300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>509900</v>
+      </c>
+      <c r="E61" s="3">
         <v>516600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>523100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>529800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>533100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>241500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>243000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>244600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>224500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>227700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>230800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>233900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>238000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>282600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>304000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>350300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>247000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>248600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>249900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>323800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>328000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>332300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>331900</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>340600</v>
       </c>
       <c r="AA61" s="3">
         <v>340600</v>
       </c>
       <c r="AB61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AC61" s="3">
         <v>344900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>349300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>311000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>315400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>319400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>323500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>356100</v>
+      </c>
+      <c r="E62" s="3">
         <v>350700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>320800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>302600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>306300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>259900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>274900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>783800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>808300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>829800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>855400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>718100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>736700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>766800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>817500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>754400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>753300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>756100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>773600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>810500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>836000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>858800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>840500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>869100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>880700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>905800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>915400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>880800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>920000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>917100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>921100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5652,8 +5801,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5750,8 +5902,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5848,106 +6003,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1499300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1562100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1245100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1326100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1329000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>895300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>851700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1402800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1401000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1451400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1525700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1429500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1682300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1636200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1693600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1666900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1704300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1706800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1632100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1601100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1630600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1686100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1642600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5982,8 +6143,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6080,8 +6242,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6178,8 +6343,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6276,8 +6444,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6374,106 +6545,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>131500</v>
+      </c>
+      <c r="E72" s="3">
         <v>87300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-8800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-51600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-24300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-40400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-51800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-68700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-399800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-461300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-477200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-512700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-535500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-562600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-584800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-610200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-631700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-650900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-650100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6570,8 +6747,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6668,8 +6848,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6766,106 +6949,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1283800</v>
+      </c>
+      <c r="E76" s="3">
         <v>1237500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1194600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1146900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1172600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1126100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1079200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1079700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1088600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1115800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1102900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1060300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>728200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>660800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>640100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>583100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>552100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>515100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>502400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>461300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>436700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>415300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>414900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>369700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>358600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>333200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>314700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>255000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>208700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>211000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>191600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6962,209 +7151,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E81" s="3">
         <v>49000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-20400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>36000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>42800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>330300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>108700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>34600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>26400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>22800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>27100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>22700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>31000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>19200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>23000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>58600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7199,88 +7397,89 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E83" s="3">
         <v>21000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>16800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>16000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>13100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7900</v>
       </c>
       <c r="Z83" s="3">
         <v>7900</v>
       </c>
       <c r="AA83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>6800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>6300</v>
       </c>
       <c r="AD83" s="3">
         <v>6300</v>
@@ -7292,13 +7491,16 @@
         <v>6300</v>
       </c>
       <c r="AG83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>4800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7395,8 +7597,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7493,8 +7698,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7591,8 +7799,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7689,8 +7900,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7787,106 +8001,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E89" s="3">
         <v>10500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>126500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>72000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-39300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-57200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>20800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>74900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>60200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>69900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>30100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>26700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>78800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>43300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>97300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>8600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>56100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>52100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7921,106 +8141,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-2100</v>
       </c>
       <c r="M91" s="3">
         <v>-2100</v>
       </c>
       <c r="N91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8117,8 +8341,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8215,106 +8442,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-303900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-550900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-184500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>582000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-84300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-24300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-93500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-67000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-11200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8349,8 +8582,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8447,8 +8681,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8545,8 +8782,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8643,8 +8883,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8741,298 +8984,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-62200</v>
+      </c>
+      <c r="E100" s="3">
         <v>292700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-115500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>363300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>62900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-35000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-167700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>26500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-25600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-48600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-55300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>113000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-18400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-86000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>117500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>12900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1700</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-900</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-117100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-126500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-164100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>491000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-37800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>38600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-119500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>108400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>14700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-29800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>37100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>16200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,451 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
-        <v>45381</v>
-      </c>
       <c r="F7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>483700</v>
+      </c>
+      <c r="E8" s="3">
         <v>501300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>465200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>469400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>448700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>423300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>399800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>429300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>370500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>354000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>307100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>349100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>285700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>296600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>287200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>345000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>268300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>258000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>369300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>444600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>364800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>372400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>343600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>445000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>362500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>379200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>351900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>387000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>348500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>349700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>340600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>284900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>300500</v>
+        <v>286100</v>
       </c>
       <c r="E9" s="3">
-        <v>282300</v>
+        <v>299600</v>
       </c>
       <c r="F9" s="3">
+        <v>279700</v>
+      </c>
+      <c r="G9" s="3">
         <v>281500</v>
       </c>
-      <c r="G9" s="3">
-        <v>280100</v>
-      </c>
       <c r="H9" s="3">
-        <v>259700</v>
+        <v>277600</v>
       </c>
       <c r="I9" s="3">
-        <v>249900</v>
+        <v>258600</v>
       </c>
       <c r="J9" s="3">
+        <v>249300</v>
+      </c>
+      <c r="K9" s="3">
         <v>267100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>237400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>229400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>203100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>217300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>189900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>194300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>182800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>219200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>176600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>169700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>255200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>301100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>258600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>264200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>260400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>309800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>274800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>281500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>261800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>306100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>263400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>273600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>252500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>177700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200800</v>
+        <v>197600</v>
       </c>
       <c r="E10" s="3">
-        <v>182900</v>
+        <v>201700</v>
       </c>
       <c r="F10" s="3">
+        <v>185500</v>
+      </c>
+      <c r="G10" s="3">
         <v>187900</v>
       </c>
-      <c r="G10" s="3">
-        <v>168600</v>
-      </c>
       <c r="H10" s="3">
-        <v>163600</v>
+        <v>171100</v>
       </c>
       <c r="I10" s="3">
-        <v>149900</v>
+        <v>164700</v>
       </c>
       <c r="J10" s="3">
+        <v>150500</v>
+      </c>
+      <c r="K10" s="3">
         <v>162200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>133100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>124600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>104000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>131800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>95800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>102300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>104400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>125800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>91700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>88300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>114100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>143500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>106200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>108200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>83200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>135200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>87700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>97700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>90100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>80900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>85100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>76100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>88100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>107200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,8 +1149,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1150,8 +1164,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>43300</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1237,8 +1251,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,210 +1355,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-200</v>
+        <v>3300</v>
       </c>
       <c r="E14" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G14" s="3">
+        <v>10100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="K14" s="3">
+        <v>13700</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M14" s="3">
+        <v>100</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P14" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
-        <v>800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
-        <v>13700</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="R14" s="3">
+        <v>200</v>
+      </c>
+      <c r="S14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T14" s="3">
+        <v>300</v>
+      </c>
+      <c r="U14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V14" s="3">
+        <v>300</v>
+      </c>
+      <c r="W14" s="3">
+        <v>600</v>
+      </c>
+      <c r="X14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>4800</v>
-      </c>
-      <c r="O14" s="3">
-        <v>24200</v>
-      </c>
-      <c r="P14" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>200</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S14" s="3">
-        <v>300</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="AA14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1000</v>
       </c>
-      <c r="U14" s="3">
-        <v>300</v>
-      </c>
-      <c r="V14" s="3">
-        <v>600</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="AC14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>2100</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>1600</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>500</v>
       </c>
       <c r="AG14" s="3">
         <v>500</v>
       </c>
       <c r="AH14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI14" s="3">
         <v>27600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E15" s="3">
         <v>16800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>14800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>1600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>100</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>200</v>
       </c>
       <c r="AH15" s="3">
         <v>200</v>
       </c>
       <c r="AI15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1574,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>426700</v>
+        <v>401900</v>
       </c>
       <c r="E17" s="3">
-        <v>400600</v>
+        <v>411900</v>
       </c>
       <c r="F17" s="3">
-        <v>406300</v>
+        <v>394600</v>
       </c>
       <c r="G17" s="3">
-        <v>391000</v>
+        <v>407800</v>
       </c>
       <c r="H17" s="3">
-        <v>372000</v>
+        <v>388700</v>
       </c>
       <c r="I17" s="3">
-        <v>350000</v>
+        <v>366800</v>
       </c>
       <c r="J17" s="3">
+        <v>349600</v>
+      </c>
+      <c r="K17" s="3">
         <v>454200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>334300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>326800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>295700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>320100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>268000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>279500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>262200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>302100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>247900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>240500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>336600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>394200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>337200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>346100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>340600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>393200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>349100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>356500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>332600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>386200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>317300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>345600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>322800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>267000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>74600</v>
+        <v>81800</v>
       </c>
       <c r="E18" s="3">
-        <v>64600</v>
+        <v>89400</v>
       </c>
       <c r="F18" s="3">
-        <v>63100</v>
+        <v>70600</v>
       </c>
       <c r="G18" s="3">
-        <v>57700</v>
+        <v>61600</v>
       </c>
       <c r="H18" s="3">
-        <v>51300</v>
+        <v>60000</v>
       </c>
       <c r="I18" s="3">
-        <v>49800</v>
+        <v>56500</v>
       </c>
       <c r="J18" s="3">
+        <v>50200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-24900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>29000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>42900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>32700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>50400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>27600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>26300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>51800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>22700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>19300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1813,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>800</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>900</v>
+      </c>
+      <c r="K20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-12200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-14500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>1500</v>
       </c>
       <c r="AD20" s="3">
         <v>1500</v>
       </c>
       <c r="AE20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>96600</v>
+        <v>97400</v>
       </c>
       <c r="E21" s="3">
-        <v>81900</v>
+        <v>104900</v>
       </c>
       <c r="F21" s="3">
-        <v>67700</v>
+        <v>86000</v>
       </c>
       <c r="G21" s="3">
-        <v>78000</v>
+        <v>72300</v>
       </c>
       <c r="H21" s="3">
-        <v>67500</v>
+        <v>74600</v>
       </c>
       <c r="I21" s="3">
-        <v>63500</v>
+        <v>68200</v>
       </c>
       <c r="J21" s="3">
+        <v>55600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>37400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>43600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>32300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>37100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>37300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>48600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>32000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>27400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>8600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>37400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>23800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>21100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E22" s="3">
         <v>12800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>10200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>5300</v>
       </c>
       <c r="Y22" s="3">
         <v>5300</v>
       </c>
       <c r="Z22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>6200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E23" s="3">
         <v>60400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>41700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-22000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>28300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>29900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>28700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>30500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>23500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>34500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>20100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>16500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>13500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E24" s="3">
         <v>15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>12400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2419,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E26" s="3">
         <v>45200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>49200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>38300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>39100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>12500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>22700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>28500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>39100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>18600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>13900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>71800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>22000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>9600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>45200</v>
+        <v>50200</v>
       </c>
       <c r="E27" s="3">
-        <v>49200</v>
+        <v>44200</v>
       </c>
       <c r="F27" s="3">
-        <v>31600</v>
+        <v>49000</v>
       </c>
       <c r="G27" s="3">
-        <v>35700</v>
+        <v>31500</v>
       </c>
       <c r="H27" s="3">
-        <v>38300</v>
+        <v>-20400</v>
       </c>
       <c r="I27" s="3">
+        <v>36000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>42800</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="L27" s="3">
+        <v>12500</v>
+      </c>
+      <c r="M27" s="3">
+        <v>19100</v>
+      </c>
+      <c r="N27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="O27" s="3">
+        <v>17600</v>
+      </c>
+      <c r="P27" s="3">
+        <v>13900</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>17700</v>
+      </c>
+      <c r="R27" s="3">
+        <v>23000</v>
+      </c>
+      <c r="S27" s="3">
+        <v>33500</v>
+      </c>
+      <c r="T27" s="3">
+        <v>15600</v>
+      </c>
+      <c r="U27" s="3">
+        <v>15200</v>
+      </c>
+      <c r="V27" s="3">
+        <v>22700</v>
+      </c>
+      <c r="W27" s="3">
+        <v>34100</v>
+      </c>
+      <c r="X27" s="3">
+        <v>21200</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>19400</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA27" s="3">
         <v>39100</v>
       </c>
-      <c r="J27" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>12500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>19100</v>
-      </c>
-      <c r="M27" s="3">
-        <v>13000</v>
-      </c>
-      <c r="N27" s="3">
-        <v>17600</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="AB27" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>18600</v>
+      </c>
+      <c r="AD27" s="3">
         <v>13900</v>
       </c>
-      <c r="P27" s="3">
-        <v>17700</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>23000</v>
-      </c>
-      <c r="R27" s="3">
-        <v>33500</v>
-      </c>
-      <c r="S27" s="3">
-        <v>15600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>15200</v>
-      </c>
-      <c r="U27" s="3">
-        <v>22700</v>
-      </c>
-      <c r="V27" s="3">
-        <v>34100</v>
-      </c>
-      <c r="W27" s="3">
-        <v>21200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>19400</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>600</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>39100</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>7300</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>18600</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>13900</v>
-      </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>71800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>22000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2722,109 +2780,115 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-56100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-2300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>3700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-9400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-6100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-1600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-11600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>316400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>91000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>11600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-7100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>7200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>11900</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>-3100</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>100</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>4400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>300</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>7100</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2924,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3025,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="L32" s="3">
+        <v>23600</v>
+      </c>
+      <c r="M32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>12200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="K32" s="3">
-        <v>23600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>14500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AD32" s="3">
         <v>-1500</v>
       </c>
       <c r="AE32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E33" s="3">
         <v>44200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>49000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>31500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-20400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>42800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>330300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>108700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>34600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>26400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>22800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>27100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>22700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>31000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>19200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>39200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>58600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>22300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3328,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E35" s="3">
         <v>44200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>49000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>31500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-20400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>42800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>330300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>108700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>34600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>26400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>22800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>27100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>22700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>31000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>19200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>39200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>58600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>22300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
-        <v>45381</v>
-      </c>
       <c r="F38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3572,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3609,132 +3695,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E41" s="3">
         <v>128100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>99400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>204800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>147800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>183400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>189800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>262800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>388200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>560100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>69100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>106900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>64000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>70700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>190200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>163100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>39000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>68800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>61900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>66700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>103700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>124300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>87200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>83500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>92700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>99600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3811,435 +3901,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>376100</v>
+      </c>
+      <c r="E43" s="3">
         <v>357900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>349600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>296400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>338100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>318000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>307100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>294300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>296300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>274400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>253400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>261000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>238400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>267600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>342700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>270600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>327200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>329900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>335900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>352300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>333300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>332100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>338100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>360300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>346400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>339500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>313000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>267500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>266600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>252000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>232700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>251700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>297700</v>
+      </c>
+      <c r="E44" s="3">
         <v>292700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>295100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>276700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>291500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>299600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>265700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>244000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>265200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>235800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>220700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>189800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>170300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>157700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>169700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>143100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>179300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>181600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>175100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>154900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>157700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>155500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>151500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>128800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>143500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>141900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>109300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>143000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>165600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>168300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>159200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>145700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>30000</v>
+        <v>26900</v>
       </c>
       <c r="E45" s="3">
-        <v>34400</v>
+        <v>26200</v>
       </c>
       <c r="F45" s="3">
-        <v>37100</v>
+        <v>28600</v>
       </c>
       <c r="G45" s="3">
-        <v>38100</v>
+        <v>29600</v>
       </c>
       <c r="H45" s="3">
-        <v>34300</v>
+        <v>28500</v>
       </c>
       <c r="I45" s="3">
-        <v>42200</v>
+        <v>25300</v>
       </c>
       <c r="J45" s="3">
+        <v>33100</v>
+      </c>
+      <c r="K45" s="3">
         <v>35000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>92800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>78600</v>
       </c>
       <c r="M45" s="3">
         <v>78600</v>
       </c>
       <c r="N45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="O45" s="3">
         <v>64400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>77700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>407000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>76200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>185500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>71400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>69900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>70200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>22800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>40500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>71300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>74300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>72500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>97700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>39600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>35100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>26500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>30600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>827600</v>
+      </c>
+      <c r="E46" s="3">
         <v>808700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>779600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>709600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>768600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>739000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>819800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>721100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>837700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>778600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>815500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>903400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1046500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>901400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>695500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>675100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>648600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>769000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>744000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>632100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>563100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>545500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>553700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>598400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>623100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>622400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>598500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>632500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>559000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>538900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>511100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>527600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4316,210 +4421,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>275100</v>
+      </c>
+      <c r="E48" s="3">
         <v>270900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>217200</v>
       </c>
-      <c r="F48" s="3">
-        <v>140500</v>
-      </c>
       <c r="G48" s="3">
+        <v>182900</v>
+      </c>
+      <c r="H48" s="3">
         <v>135100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>134700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>110300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>156200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>107000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>110700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>155000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>108000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>113000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>186600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>147300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>187600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>178100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>176900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>209800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>202000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>199900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>204600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>184200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>185000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>188200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>185800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>186600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>188800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>191600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>193600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>195500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1585000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1587700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1605100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1385600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1362800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1385500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>854200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>856900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>852300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>875800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>896500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>872800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>741200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>735000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>800500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>673600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>792800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>697500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>694200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>701000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>660300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>660600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>661900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>592800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>594100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>595200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>478100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>463500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>463100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>462500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>459900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>458300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4619,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4720,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>115800</v>
+        <v>116000</v>
       </c>
       <c r="E52" s="3">
-        <v>197700</v>
+        <v>112300</v>
       </c>
       <c r="F52" s="3">
-        <v>204000</v>
+        <v>193700</v>
       </c>
       <c r="G52" s="3">
-        <v>206500</v>
+        <v>157600</v>
       </c>
       <c r="H52" s="3">
-        <v>242400</v>
+        <v>202100</v>
       </c>
       <c r="I52" s="3">
-        <v>237100</v>
+        <v>236000</v>
       </c>
       <c r="J52" s="3">
+        <v>231400</v>
+      </c>
+      <c r="K52" s="3">
         <v>196700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>685500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>725600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>744500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>697400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>594100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>661100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>614400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1447500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>621000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>611800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>606800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>591600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>637000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>661300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>681200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>682100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>704200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>718000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>749700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>757800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>721900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>736400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>733800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>731100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4922,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2806000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2783100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2799600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2439700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2473000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2501600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2021400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1930900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2482500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2489600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2567200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2628600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2489800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2410500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2297000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2333700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2250000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2256400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2221900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2134500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2062400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2067300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2101400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5060,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5097,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E57" s="3">
         <v>128200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>118700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>131700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>131000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>120000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>124500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>125200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>116200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>111000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>119600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>112300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>86800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>135000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>102100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>134500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>137900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>148000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>141600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>132500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>135900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>142200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>153600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>141200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>150700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>145000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>159700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>143300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>140800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>133100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>137600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>280400</v>
+        <v>82500</v>
       </c>
       <c r="E58" s="3">
+        <v>290600</v>
+      </c>
+      <c r="F58" s="3">
         <v>337800</v>
       </c>
-      <c r="F58" s="3">
-        <v>35200</v>
-      </c>
       <c r="G58" s="3">
+        <v>46500</v>
+      </c>
+      <c r="H58" s="3">
         <v>144100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>142500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>72400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>178700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>108900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>121800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>113600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>270900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>262900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>143600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>59100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>73600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>89200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>49900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>122400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>133300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>57000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>52000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>35100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>32700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>224700</v>
+        <v>81900</v>
       </c>
       <c r="E59" s="3">
-        <v>205600</v>
+        <v>82100</v>
       </c>
       <c r="F59" s="3">
-        <v>247300</v>
+        <v>88200</v>
       </c>
       <c r="G59" s="3">
-        <v>217900</v>
+        <v>103700</v>
       </c>
       <c r="H59" s="3">
-        <v>216100</v>
+        <v>77800</v>
       </c>
       <c r="I59" s="3">
-        <v>201500</v>
+        <v>92000</v>
       </c>
       <c r="J59" s="3">
+        <v>87500</v>
+      </c>
+      <c r="K59" s="3">
         <v>205500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>246900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>236900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>267900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>304700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>351500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>442100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>342900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>361600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>314100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>295200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>291200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>323400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>275200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>257100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>263600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>266700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>263400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>259900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>271500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>293800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>285700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>292500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>282700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>306000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>446300</v>
+      </c>
+      <c r="E60" s="3">
         <v>633300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>694800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>401200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>493700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>489600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>393900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>333800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>374400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>368200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>393900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>439500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>477500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>707600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>586800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>572100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>562200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>704000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>702100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>608600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>466800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>466600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>495000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>470200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>527000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>543900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>428200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>461000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>486000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>485300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>450900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>476300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>509900</v>
+        <v>703900</v>
       </c>
       <c r="E61" s="3">
+        <v>549300</v>
+      </c>
+      <c r="F61" s="3">
         <v>516600</v>
       </c>
-      <c r="F61" s="3">
-        <v>523100</v>
-      </c>
       <c r="G61" s="3">
+        <v>551600</v>
+      </c>
+      <c r="H61" s="3">
         <v>529800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>533100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>241500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>243000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>244600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>224500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>227700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>230800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>233900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>238000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>282600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>304000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>350300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>247000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>248600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>249900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>323800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>328000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>332300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>340600</v>
       </c>
       <c r="AB61" s="3">
         <v>340600</v>
       </c>
       <c r="AC61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AD61" s="3">
         <v>344900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>349300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>311000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>315400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>319400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>323500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>356100</v>
+        <v>186000</v>
       </c>
       <c r="E62" s="3">
-        <v>350700</v>
+        <v>210100</v>
       </c>
       <c r="F62" s="3">
-        <v>320800</v>
+        <v>237100</v>
       </c>
       <c r="G62" s="3">
-        <v>302600</v>
+        <v>113900</v>
       </c>
       <c r="H62" s="3">
-        <v>306300</v>
+        <v>235700</v>
       </c>
       <c r="I62" s="3">
-        <v>259900</v>
+        <v>226500</v>
       </c>
       <c r="J62" s="3">
+        <v>225000</v>
+      </c>
+      <c r="K62" s="3">
         <v>274900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>783800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>808300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>829800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>855400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>718100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>736700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>766800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>817500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>754400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>753300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>756100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>773600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>810500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>836000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>858800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>840500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>869100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>880700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>905800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>915400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>880800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>920000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>917100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>921100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5804,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5905,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6006,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1447800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1499300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1562100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1245100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1326100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1329000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>895300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>851700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1402800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1401000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1451400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1525700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1429500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1682300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1636200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1693600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1666900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1704300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1706800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1632100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1601100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1630600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1686100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6144,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6245,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6346,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6447,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6548,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>181700</v>
+      </c>
+      <c r="E72" s="3">
         <v>131500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>87300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>38300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-51600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-24300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-40400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-68700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-399800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-461300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-477200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-512700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-535500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-562600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-584800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-610200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-631700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-650900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6750,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6851,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6952,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1358200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1283800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1237500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1194600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1146900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1172600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1126100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1079200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1079700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1088600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1115800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1102900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1060300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>728200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>660800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>640100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>583100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>552100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>515100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>502400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>461300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>436700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>415300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>414900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>369700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>358600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>333200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>314700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>255000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>208700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>211000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>191600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7154,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
-        <v>45381</v>
-      </c>
       <c r="F80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E81" s="3">
         <v>44200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>49000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>31500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-20400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>42800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>330300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>108700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>34600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>26400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>22800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>27100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>22700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>31000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>19200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>39200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>58600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>22300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7398,91 +7596,92 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>23400</v>
+        <v>5100</v>
       </c>
       <c r="E83" s="3">
-        <v>21000</v>
+        <v>4500</v>
       </c>
       <c r="F83" s="3">
-        <v>16800</v>
+        <v>4400</v>
       </c>
       <c r="G83" s="3">
-        <v>19700</v>
+        <v>4000</v>
       </c>
       <c r="H83" s="3">
-        <v>16000</v>
+        <v>4600</v>
       </c>
       <c r="I83" s="3">
-        <v>10700</v>
+        <v>4500</v>
       </c>
       <c r="J83" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K83" s="3">
         <v>9500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>13100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8100</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7900</v>
       </c>
       <c r="AA83" s="3">
         <v>7900</v>
       </c>
       <c r="AB83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>6800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>6300</v>
       </c>
       <c r="AE83" s="3">
         <v>6300</v>
@@ -7494,13 +7693,16 @@
         <v>6300</v>
       </c>
       <c r="AH83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>4800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7600,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7701,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7802,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7903,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8004,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E89" s="3">
         <v>57500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>126500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>72000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-39300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-57200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>20800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>74900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>60200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>69900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>30100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>78800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>43300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>97300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>56100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>52100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8142,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-2100</v>
       </c>
       <c r="N91" s="3">
         <v>-2100</v>
       </c>
       <c r="O91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8344,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8445,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E94" s="3">
         <v>32400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-303900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-550900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-184500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>582000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-84300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-93500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-67000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8583,31 +8816,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8684,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8785,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8886,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8987,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-62200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>292700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-115500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>363300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>62900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-35000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-167700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>26500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-25600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-48600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-55300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>113000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-18400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-19000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>117500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>12900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>400</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="R101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="S101" s="3">
+        <v>600</v>
+      </c>
+      <c r="T101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>900</v>
       </c>
-      <c r="G101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J101" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>400</v>
-      </c>
-      <c r="O101" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P101" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>3100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>1000</v>
-      </c>
-      <c r="X101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>900</v>
-      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E102" s="3">
         <v>27500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-117100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-126500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-164100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>491000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-119500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>27100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>108400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>14700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-29800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>37100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,464 +656,476 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>533700</v>
+      </c>
+      <c r="E8" s="3">
         <v>483700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>501300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>465200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>469400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>448700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>423300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>399800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>429300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>370500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>354000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>307100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>349100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>285700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>296600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>287200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>345000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>268300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>258000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>369300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>444600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>364800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>372400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>343600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>445000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>362500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>379200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>351900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>387000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>348500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>349700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>340600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>284900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>315600</v>
+      </c>
+      <c r="E9" s="3">
         <v>286100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>299600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>279700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>281500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>277600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>258600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>249300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>267100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>237400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>229400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>203100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>217300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>189900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>194300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>182800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>219200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>176600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>169700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>255200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>301100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>258600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>264200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>260400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>309800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>274800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>281500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>261800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>306100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>263400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>273600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>252500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>177700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>218100</v>
+      </c>
+      <c r="E10" s="3">
         <v>197600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>201700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>185500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>187900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>171100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>164700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>150500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>162200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>133100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>124600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>104000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>131800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>95800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>102300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>104400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>125800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>91700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>88300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>114100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>143500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>106200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>108200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>83200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>135200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>87700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>97700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>90100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>80900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>85100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>76100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>88100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>107200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,13 +1162,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>46300</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1164,11 +1177,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>43300</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1254,8 +1267,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,216 +1374,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-18100</v>
+      </c>
+      <c r="E14" s="3">
         <v>3300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10600</v>
       </c>
-      <c r="G14" s="3">
-        <v>10100</v>
-      </c>
       <c r="H14" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I14" s="3">
         <v>2500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>4800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>500</v>
       </c>
       <c r="AH14" s="3">
         <v>500</v>
       </c>
       <c r="AI14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>27600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E15" s="3">
         <v>16600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>9300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>1600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>100</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>200</v>
       </c>
       <c r="AI15" s="3">
         <v>200</v>
       </c>
       <c r="AJ15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AK15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,216 +1626,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>461700</v>
+      </c>
+      <c r="E17" s="3">
         <v>401900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>411900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>394600</v>
       </c>
-      <c r="G17" s="3">
-        <v>407800</v>
-      </c>
       <c r="H17" s="3">
+        <v>402700</v>
+      </c>
+      <c r="I17" s="3">
         <v>388700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>366800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>349600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>454200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>334300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>326800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>295700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>320100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>268000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>279500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>262200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>302100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>247900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>240500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>336600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>394200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>337200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>346100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>340600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>393200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>349100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>356500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>332600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>386200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>317300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>345600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>322800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>267000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E18" s="3">
         <v>81800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>89400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>70600</v>
       </c>
-      <c r="G18" s="3">
-        <v>61600</v>
-      </c>
       <c r="H18" s="3">
+        <v>66700</v>
+      </c>
+      <c r="I18" s="3">
         <v>60000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>29000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>42900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>32700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>50400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>27600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>26300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>51800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>22700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>19300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,528 +1879,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-23600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>1500</v>
       </c>
       <c r="AE20" s="3">
         <v>1500</v>
       </c>
       <c r="AF20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E21" s="3">
         <v>97400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>104900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>86000</v>
       </c>
-      <c r="G21" s="3">
-        <v>72300</v>
-      </c>
       <c r="H21" s="3">
+        <v>77400</v>
+      </c>
+      <c r="I21" s="3">
         <v>74600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>68200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-10500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>33600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>32500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>43600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>47400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>32300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>45700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>37100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>37300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>48600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>32000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>27400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>23800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>21100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="3">
         <v>12100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>5300</v>
       </c>
       <c r="Z22" s="3">
         <v>5300</v>
       </c>
       <c r="AA22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AB22" s="3">
         <v>6200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E23" s="3">
         <v>66000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>60400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>48100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>46100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-22000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>28300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>29900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>30500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>23500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>34500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>16500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>13500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E24" s="3">
         <v>15100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>12400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,216 +2519,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E26" s="3">
         <v>50900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>45200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>49200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>31600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>38300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>39100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>28500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>21200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>18600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>13900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>71800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>22000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>10300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E27" s="3">
         <v>50200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>44200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>49000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>31500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-20400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>42800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>22700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>34100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>21200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>13900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>71800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,112 +2840,118 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-200</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-56100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>3700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-9400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-6100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-1600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-11600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>316400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>91000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>11600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-7100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>7200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>11900</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>300</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>4400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>300</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>7100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,216 +3161,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>23600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>11100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AE32" s="3">
         <v>-1500</v>
       </c>
       <c r="AF32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E33" s="3">
         <v>50200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>44200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>49000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>31500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-20400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>42800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>330300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>108700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>34600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>26400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>22800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>27100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>31000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>21500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>19200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>6600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>58600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>17400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,221 +3482,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E35" s="3">
         <v>50200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>44200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>49000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>31500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-20400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>42800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>330300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>108700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>34600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>26400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>22800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>27100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>31000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>21500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>19200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>6600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>58600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>17400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,139 +3781,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E41" s="3">
         <v>124800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>128100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>99400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>87100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>204800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>147800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>183400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>189800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>262800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>388200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>560100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>69100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>106900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>64000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>70700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>190200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>163100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>54700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>49300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>34600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>39000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>68800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>61900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>66700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>103700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>124300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>87200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>83500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>92700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>99600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E42" s="3">
         <v>2100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3904,429 +3993,444 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>324900</v>
+      </c>
+      <c r="E43" s="3">
         <v>376100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>357900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>349600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>296400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>338100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>318000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>307100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>294300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>296300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>274400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>253400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>261000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>238400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>267600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>342700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>270600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>327200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>329900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>335900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>352300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>333300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>332100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>338100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>360300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>346400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>339500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>313000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>267500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>266600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>252000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>232700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>251700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>271000</v>
+      </c>
+      <c r="E44" s="3">
         <v>297700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>292700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>295100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>276700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>291500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>299600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>265700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>244000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>265200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>235800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>220700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>189800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>170300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>157700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>169700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>143100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>179300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>181600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>175100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>154900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>157700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>155500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>151500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>128800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>143500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>141900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>109300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>143000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>165600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>168300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>159200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>145700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E45" s="3">
         <v>26900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>35000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>92800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>78600</v>
       </c>
       <c r="N45" s="3">
         <v>78600</v>
       </c>
       <c r="O45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="P45" s="3">
         <v>64400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>77700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>407000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>76200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>185500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>71400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>67300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>69900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>70200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>22800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>71300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>74300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>72500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>97700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>39600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>35100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>26500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>30600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>784300</v>
+      </c>
+      <c r="E46" s="3">
         <v>827600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>808700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>779600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>709600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>768600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>739000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>819800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>721100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>837700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>778600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>815500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>903400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1046500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>901400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>695500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>675100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>648600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>769000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>744000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>632100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>563100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>545500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>553700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>598400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>623100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>622400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>598500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>632500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>559000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>538900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>511100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>527600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>700</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4337,18 +4441,18 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>1200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3100</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4424,216 +4528,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>275900</v>
+      </c>
+      <c r="E48" s="3">
         <v>275100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>270900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>217200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>182900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>135100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>134700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>110300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>156200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>107000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>109600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>110700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>155000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>108000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>113000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>186600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>147300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>187600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>178100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>176900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>209800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>202000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>199900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>204600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>184200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>185000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>188200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>185800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>186600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>188800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>191600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>193600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>195500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1537500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1585000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1587700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1605100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1385600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1362800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1385500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>854200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>856900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>852300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>875800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>896500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>872800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>741200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>735000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>800500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>673600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>792800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>697500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>694200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>701000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>660300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>660600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>661900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>592800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>594100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>595200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>478100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>463500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>463100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>462500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>459900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>458300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,112 +4956,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>111100</v>
+      </c>
+      <c r="E52" s="3">
         <v>116000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>112300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>193700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>157600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>202100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>236000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>231400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>196700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>685500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>725600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>744500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>697400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>594100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>661100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>614400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1447500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>621000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>611800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>606800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>591600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>637000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>661300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>681200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>682100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>704200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>718000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>749700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>757800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>721900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>736400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>733800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>731100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2714500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2806000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2783100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2799600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2439700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2473000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2501600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2021400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1930900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2482500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2489600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2567200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2628600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2489800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2410500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2297000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2333700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2250000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2256400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2221900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2134500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2062400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2067300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2101400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E57" s="3">
         <v>139400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>128200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>151400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>118700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>131700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>131000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>124500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>125200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>116200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>111000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>119600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>112300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>86800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>135000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>102100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>134500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>137900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>148000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>141600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>132500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>135900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>142200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>153600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>141200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>150700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>145000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>159700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>143300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>140800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>133100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>137600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E58" s="3">
         <v>82500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>290600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>337800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>46500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>144100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>142500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>72400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>15100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>178700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>108900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>121800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>113600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>270900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>262900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>143600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>59100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>73600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>89200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>49900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>122400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>133300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>57000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>52000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>35100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E59" s="3">
         <v>81900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>88200</v>
       </c>
-      <c r="G59" s="3">
-        <v>103700</v>
-      </c>
       <c r="H59" s="3">
+        <v>95200</v>
+      </c>
+      <c r="I59" s="3">
         <v>77800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>92000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>87500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>205500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>246900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>236900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>267900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>304700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>351500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>442100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>342900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>361600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>314100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>295200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>291200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>323400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>275200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>257100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>263600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>266700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>263400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>259900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>271500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>293800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>285700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>292500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>282700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>306000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>418300</v>
+      </c>
+      <c r="E60" s="3">
         <v>446300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>633300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>694800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>401200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>493700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>489600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>393900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>333800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>374400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>368200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>393900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>439500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>477500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>707600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>586800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>572100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>562200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>704000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>702100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>608600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>466800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>466600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>495000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>470200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>527000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>543900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>428200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>461000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>486000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>485300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>450900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>476300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>621500</v>
+      </c>
+      <c r="E61" s="3">
         <v>703900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>549300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>516600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>551600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>529800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>533100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>241500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>243000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>244600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>224500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>227700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>230800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>233900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>238000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>282600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>304000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>350300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>247000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>248600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>249900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>323800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>328000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>332300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>340600</v>
       </c>
       <c r="AC61" s="3">
         <v>340600</v>
       </c>
       <c r="AD61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AE61" s="3">
         <v>344900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>349300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>311000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>315400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>319400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>323500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E62" s="3">
         <v>186000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>210100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>237100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>113900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>235700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>226500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>225000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>274900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>783800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>808300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>829800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>855400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>718100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>736700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>766800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>817500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>754400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>753300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>756100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>773600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>810500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>836000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>858800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>840500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>869100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>880700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>905800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>915400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>880800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>920000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>917100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>921100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1330100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1447800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1499300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1562100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1245100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1326100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1329000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>895300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>851700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1402800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1401000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1451400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1525700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1429500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1682300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1636200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1693600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1666900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1704300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1706800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1632100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1601100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1630600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1686100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>238800</v>
+      </c>
+      <c r="E72" s="3">
         <v>181700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>131500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>87300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>38300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-51600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-40400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-68700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-399800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-461300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-477200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-512700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-535500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-562600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-584800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-610200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-631700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-650900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1384400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1358200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1283800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1237500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1194600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1146900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1172600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1126100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1079200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1079700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1088600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1115800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1102900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1060300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>728200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>660800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>640100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>583100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>552100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>515100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>502400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>461300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>436700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>415300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>414900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>369700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>358600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>333200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>314700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>255000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>208700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>211000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>191600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,221 +7534,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>57100</v>
+      </c>
+      <c r="E81" s="3">
         <v>50200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>44200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>49000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>31500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-20400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>42800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>330300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>108700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>34600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>26400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>22800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>27100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>31000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>21500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>19200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>6600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>58600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>17400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,94 +7794,95 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E83" s="3">
         <v>5100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>13100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8100</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>7900</v>
       </c>
       <c r="AB83" s="3">
         <v>7900</v>
       </c>
       <c r="AC83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>6800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>6300</v>
       </c>
       <c r="AF83" s="3">
         <v>6300</v>
@@ -7696,13 +7894,16 @@
         <v>6300</v>
       </c>
       <c r="AI83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,112 +8434,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>166500</v>
+      </c>
+      <c r="E89" s="3">
         <v>51400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>126500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>72000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-39300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-57200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>20800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>74900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>60200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>69900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>78800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>43300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>97300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>52100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,112 +8582,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2100</v>
       </c>
       <c r="O91" s="3">
         <v>-2100</v>
       </c>
       <c r="P91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,112 +8901,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>32400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-303900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-550900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-184500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>582000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-84300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-24300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-93500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-67000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-74700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8843,8 +9076,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8921,8 +9154,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,316 +9475,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-123800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-53600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-62200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>292700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-115500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>363300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>62900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-35000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-167700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>26500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-25600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-48600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>113000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-19000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>32700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>117500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>12900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-900</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-117100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>55600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-30200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-74300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-126500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-164100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>491000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-37800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-119500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>27100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>108400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>14700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>37100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,476 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
-        <v>45382</v>
-      </c>
       <c r="H7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>482600</v>
+      </c>
+      <c r="E8" s="3">
         <v>533700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>483700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>501300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>465200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>469400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>448700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>423300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>399800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>429300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>370500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>354000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>307100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>349100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>285700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>296600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>287200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>345000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>268300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>258000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>369300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>444600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>364800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>372400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>343600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>445000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>362500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>379200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>351900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>387000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>348500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>349700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>340600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>284900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>286400</v>
+      </c>
+      <c r="E9" s="3">
         <v>315600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>286100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>299600</v>
       </c>
-      <c r="G9" s="3">
-        <v>279700</v>
-      </c>
       <c r="H9" s="3">
+        <v>281400</v>
+      </c>
+      <c r="I9" s="3">
         <v>281500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>277600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>258600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>249300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>267100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>237400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>229400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>203100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>217300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>189900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>194300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>182800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>219200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>176600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>169700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>255200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>301100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>258600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>264200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>260400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>309800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>274800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>281500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>261800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>306100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>263400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>273600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>177700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>196200</v>
+      </c>
+      <c r="E10" s="3">
         <v>218100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>197600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>201700</v>
       </c>
-      <c r="G10" s="3">
-        <v>185500</v>
-      </c>
       <c r="H10" s="3">
+        <v>183800</v>
+      </c>
+      <c r="I10" s="3">
         <v>187900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>171100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>164700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>150500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>162200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>133100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>124600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>104000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>131800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>95800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>102300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>104400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>125800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>91700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>88300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>114100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>143500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>106200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>108200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>83200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>135200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>87700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>97700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>90100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>80900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>85100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>76100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>88100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>107200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,16 +1176,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>46300</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1180,11 +1194,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>43300</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1270,8 +1284,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,222 +1394,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-18100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15200</v>
       </c>
-      <c r="G14" s="3">
-        <v>10600</v>
-      </c>
       <c r="H14" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I14" s="3">
         <v>15200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>24200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>500</v>
       </c>
       <c r="AI14" s="3">
         <v>500</v>
       </c>
       <c r="AJ14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK14" s="3">
         <v>27600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E15" s="3">
         <v>16300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>11500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>6500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>1600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>100</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>200</v>
       </c>
       <c r="AJ15" s="3">
         <v>200</v>
       </c>
       <c r="AK15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>410200</v>
+      </c>
+      <c r="E17" s="3">
         <v>461700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>401900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>411900</v>
       </c>
-      <c r="G17" s="3">
-        <v>394600</v>
-      </c>
       <c r="H17" s="3">
+        <v>399500</v>
+      </c>
+      <c r="I17" s="3">
         <v>402700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>388700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>366800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>349600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>454200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>334300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>326800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>295700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>320100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>268000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>279500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>262200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>302100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>247900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>240500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>336600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>394200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>337200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>346100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>340600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>393200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>349100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>356500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>332600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>386200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>317300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>345600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>322800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>267000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E18" s="3">
         <v>72000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>81800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>89400</v>
       </c>
-      <c r="G18" s="3">
-        <v>70600</v>
-      </c>
       <c r="H18" s="3">
+        <v>65700</v>
+      </c>
+      <c r="I18" s="3">
         <v>66700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>60000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>29000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>25000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>42900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>20400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>32700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>50400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>27600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>26300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>51800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>22700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>17900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,543 +1913,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>2100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-23600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>1500</v>
       </c>
       <c r="AF20" s="3">
         <v>1500</v>
       </c>
       <c r="AG20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E21" s="3">
         <v>86200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>97400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>104900</v>
       </c>
-      <c r="G21" s="3">
-        <v>86000</v>
-      </c>
       <c r="H21" s="3">
+        <v>81100</v>
+      </c>
+      <c r="I21" s="3">
         <v>77400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>74600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>68200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>55600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>23900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>33600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>43600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>47400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>32300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>37100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>37300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>48600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>32000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>27400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>37400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>8600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>23800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>21100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E22" s="3">
         <v>11000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>5300</v>
       </c>
       <c r="AA22" s="3">
         <v>5300</v>
       </c>
       <c r="AB22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AC22" s="3">
         <v>6200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E23" s="3">
         <v>77900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>60400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>41700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>46100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>23500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>30500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>23500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>34500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>16500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>26800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>13500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>12600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>21400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>10100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>12400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E26" s="3">
         <v>56500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>50900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>45200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>49200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>35700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>38300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>39100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>17700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>28500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>21200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>71800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>22000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>9600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E27" s="3">
         <v>57100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>50200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>44200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>49000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>17700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>22700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>34100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>21200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>13900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>71800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,115 +2901,121 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E29" s="3">
         <v>600</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-56100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>3700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-2500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-9400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-1600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>316400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>91000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>11600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>7200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>11900</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>300</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-700</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>4400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>7100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>23600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>11100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AF32" s="3">
         <v>-1500</v>
       </c>
       <c r="AG32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E33" s="3">
         <v>57100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>50200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>44200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>49000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-20400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>42800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>330300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>108700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>34600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>22800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>27100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>22700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>31000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>21500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>19200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>6600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>23000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>58600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E35" s="3">
         <v>57100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>50200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>44200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>49000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-20400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>42800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>330300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>108700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>34600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>22800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>27100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>22700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>31000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>21500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>19200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>6600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>23000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>58600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
-        <v>45382</v>
-      </c>
       <c r="H38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,145 +3868,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>177800</v>
+      </c>
+      <c r="E41" s="3">
         <v>156900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>124800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>128100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>99400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>87100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>204800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>147800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>183400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>189800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>262800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>388200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>560100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>69100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>106900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>64000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>70700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>163100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>54700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>49300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>34600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>39000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>61900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>66700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>103700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>124300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>87200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>83500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>92700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>99600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E42" s="3">
         <v>2700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3996,444 +4086,459 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>357100</v>
+      </c>
+      <c r="E43" s="3">
         <v>324900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>376100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>357900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>349600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>296400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>338100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>318000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>307100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>294300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>296300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>274400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>253400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>261000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>238400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>267600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>342700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>270600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>327200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>329900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>335900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>352300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>333300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>332100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>338100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>360300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>346400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>339500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>313000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>267500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>266600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>252000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>232700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>251700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>308100</v>
+      </c>
+      <c r="E44" s="3">
         <v>271000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>297700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>292700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>295100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>276700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>291500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>299600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>265700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>244000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>265200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>235800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>220700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>189800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>170300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>157700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>169700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>143100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>179300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>181600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>175100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>154900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>157700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>155500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>151500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>128800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>143500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>141900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>109300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>143000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>165600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>168300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>159200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>145700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>61600</v>
+      </c>
+      <c r="E45" s="3">
         <v>28800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>25300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>35000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>92800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>78600</v>
       </c>
       <c r="O45" s="3">
         <v>78600</v>
       </c>
       <c r="P45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>64400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>77700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>407000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>76200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>185500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>71400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>67300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>69900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>70200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>22800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>23300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>40500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>71300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>74300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>72500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>97700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>39600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>35100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>26500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>30600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>906800</v>
+      </c>
+      <c r="E46" s="3">
         <v>784300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>827600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>808700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>779600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>709600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>768600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>739000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>819800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>721100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>837700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>778600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>815500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>903400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1046500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>901400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>695500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>675100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>648600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>769000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>744000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>632100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>563100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>545500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>553700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>598400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>623100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>622400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>598500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>632500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>559000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>538900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>511100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>527600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
         <v>700</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
+      <c r="E47" s="3">
+        <v>700</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -4444,18 +4549,18 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>1200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3100</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4531,222 +4636,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E48" s="3">
         <v>275900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>275100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>270900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>217200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>182900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>135100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>134700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>110300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>156200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>107000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>109600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>110700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>155000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>108000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>113000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>186600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>147300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>187600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>178100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>176900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>209800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>202000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>199900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>204600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>184200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>185000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>188200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>185800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>186600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>188800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>191600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>193600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>195500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1803900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1537500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1585000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1587700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1605100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1385600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1362800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1385500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>854200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>856900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>852300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>875800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>896500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>872800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>741200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>735000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>800500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>673600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>792800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>697500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>694200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>701000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>660300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>660600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>661900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>592800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>594100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>595200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>478100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>463500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>463100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>462500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>459900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>458300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,115 +5076,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>199900</v>
+      </c>
+      <c r="E52" s="3">
         <v>111100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>116000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>193700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>157600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>202100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>236000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>231400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>196700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>685500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>725600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>744500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>697400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>594100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>661100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>614400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1447500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>621000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>611800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>606800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>591600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>637000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>661300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>681200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>682100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>704200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>718000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>749700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>757800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>721900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>736400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>733800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>731100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3137500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2714500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2806000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2783100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2799600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2439700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2473000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2501600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2021400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1930900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2482500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2489600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2567200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2628600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2489800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2410500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2297000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2333700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2250000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2256400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2221900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2134500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2062400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2067300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2101400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E57" s="3">
         <v>128100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>139400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>128200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>151400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>118700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>131700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>131000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>120000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>124500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>125200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>116200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>111000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>119600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>112300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>86800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>135000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>102100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>134500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>137900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>148000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>141600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>132500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>135900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>142200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>153600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>141200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>150700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>145000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>159700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>143300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>140800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>133100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>137600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E58" s="3">
         <v>48800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>290600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>337800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>46500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>144100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>142500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>72400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>178700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>108900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>121800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>113600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>270900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>262900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>143600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>59100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>73600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>89200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>49900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>122400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>133300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>57000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>52000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>35100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>32700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E59" s="3">
         <v>100600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>81900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>88200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>95200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>92000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>87500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>205500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>246900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>236900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>267900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>304700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>351500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>442100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>342900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>361600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>314100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>295200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>291200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>323400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>275200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>257100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>263600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>266700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>263400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>259900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>271500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>293800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>285700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>292500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>282700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>306000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>482900</v>
+      </c>
+      <c r="E60" s="3">
         <v>418300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>446300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>633300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>694800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>401200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>493700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>489600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>393900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>333800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>374400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>368200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>393900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>439500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>477500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>707600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>586800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>572100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>562200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>704000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>702100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>608600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>466800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>466600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>495000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>470200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>527000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>543900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>428200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>461000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>486000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>485300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>450900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>476300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>872000</v>
+      </c>
+      <c r="E61" s="3">
         <v>621500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>703900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>549300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>516600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>551600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>529800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>533100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>241500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>243000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>244600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>224500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>227700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>230800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>233900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>238000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>282600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>304000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>350300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>247000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>248600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>249900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>323800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>328000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>332300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>340600</v>
       </c>
       <c r="AD61" s="3">
         <v>340600</v>
       </c>
       <c r="AE61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AF61" s="3">
         <v>344900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>349300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>311000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>315400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>319400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>323500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>236700</v>
+      </c>
+      <c r="E62" s="3">
         <v>94300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>186000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>210100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>237100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>113900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>235700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>226500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>225000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>274900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>783800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>808300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>829800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>855400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>718100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>736700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>766800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>817500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>754400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>753300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>756100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>773600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>810500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>836000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>858800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>840500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>869100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>880700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>905800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>915400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>880800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>920000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>917100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>921100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1694100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1330100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1447800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1499300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1562100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1245100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1326100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1329000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>895300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>851700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1402800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1401000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1451400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1525700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1429500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1682300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1636200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1693600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1666900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1704300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1706800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1632100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1601100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1630600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1686100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E72" s="3">
         <v>238800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>181700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>131500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>87300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-51600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-24300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-40400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-68700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-399800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-461300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-477200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-512700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-535500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-562600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-584800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-610200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-631700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-650900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1443400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1384400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1358200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1283800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1237500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1194600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1146900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1172600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1126100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1079200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1079700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1088600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1115800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1102900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1060300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>728200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>660800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>640100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>583100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>552100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>515100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>502400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>461300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>436700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>415300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>414900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>369700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>358600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>333200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>314700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>255000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>208700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>211000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>191600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
-        <v>45382</v>
-      </c>
       <c r="H80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E81" s="3">
         <v>57100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>50200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>44200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>49000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-20400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>42800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>330300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>108700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>34600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>22800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>27100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>22700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>31000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>21500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>19200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>6600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>23000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>58600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,97 +7993,98 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>14000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8100</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>7900</v>
       </c>
       <c r="AC83" s="3">
         <v>7900</v>
       </c>
       <c r="AD83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AE83" s="3">
         <v>6800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>6300</v>
       </c>
       <c r="AG83" s="3">
         <v>6300</v>
@@ -7897,13 +8096,16 @@
         <v>6300</v>
       </c>
       <c r="AJ83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AK83" s="3">
         <v>4800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E89" s="3">
         <v>166500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>51400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>126500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-26300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-39300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-57200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>20800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>74900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>60200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>69900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>26700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>78800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>43300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>97300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>8600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>52100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-2100</v>
       </c>
       <c r="P91" s="3">
         <v>-2100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-306600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>32400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-303900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-550900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-184500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>582000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-84300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-93500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-67000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-11200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-74700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9079,8 +9313,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9157,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>335700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-123800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-53600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-62200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>292700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>363300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>62900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-35000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-167700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>26500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-25600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-48600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-55300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>113000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-18400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>32700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>117500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>12900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E101" s="3">
         <v>900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1700</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-900</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E102" s="3">
         <v>32000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-117100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>55600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-74300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-126500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-164100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>491000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-37800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-119500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>108400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>14700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>37100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>16200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,489 +656,502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>552400</v>
+      </c>
+      <c r="E8" s="3">
         <v>482600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>533700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>483700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>501300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>465200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>469400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>448700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>423300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>399800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>429300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>370500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>354000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>307100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>349100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>285700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>296600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>287200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>345000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>268300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>258000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>369300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>444600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>364800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>372400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>343600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>445000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>362500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>379200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>351900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>387000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>348500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>349700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>340600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>284900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E9" s="3">
         <v>286400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>315600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>286100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>299600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>281400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>281500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>277600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>258600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>249300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>267100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>237400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>229400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>203100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>217300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>189900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>194300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>182800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>219200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>176600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>169700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>255200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>301100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>258600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>264200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>260400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>309800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>274800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>281500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>261800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>306100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>263400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>273600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>252500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>177700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>229400</v>
+      </c>
+      <c r="E10" s="3">
         <v>196200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>218100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>197600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>201700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>183800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>187900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>171100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>150500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>162200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>133100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>124600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>104000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>131800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>95800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>102300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>104400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>125800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>91700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>88300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>114100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>143500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>106200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>108200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>83200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>135200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>87700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>97700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>90100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>80900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>85100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>76100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>88100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>107200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,19 +1190,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>46300</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1197,11 +1211,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>43300</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1287,8 +1301,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1397,228 +1414,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-18100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J14" s="3">
         <v>15200</v>
       </c>
-      <c r="H14" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I14" s="3">
-        <v>15200</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-3000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>4800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>24200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>500</v>
       </c>
       <c r="AJ14" s="3">
         <v>500</v>
       </c>
       <c r="AK14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL14" s="3">
         <v>27600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E15" s="3">
         <v>19700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>16300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>16600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>7100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>5600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>5500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>6500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>4000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>1600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>1500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>100</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>200</v>
       </c>
       <c r="AK15" s="3">
         <v>200</v>
       </c>
       <c r="AL15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AM15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,228 +1680,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>458200</v>
+      </c>
+      <c r="E17" s="3">
         <v>410200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>461700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>401900</v>
       </c>
-      <c r="G17" s="3">
-        <v>411900</v>
-      </c>
       <c r="H17" s="3">
+        <v>425100</v>
+      </c>
+      <c r="I17" s="3">
         <v>399500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>402700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>388700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>366800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>349600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>454200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>334300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>326800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>295700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>320100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>268000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>279500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>262200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>302100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>247900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>240500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>336600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>394200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>337200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>346100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>340600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>393200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>349100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>356500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>332600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>386200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>317300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>345600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>322800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>267000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E18" s="3">
         <v>72400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>72000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>81800</v>
       </c>
-      <c r="G18" s="3">
-        <v>89400</v>
-      </c>
       <c r="H18" s="3">
+        <v>76200</v>
+      </c>
+      <c r="I18" s="3">
         <v>65700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>66700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>60000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>56500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>29000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>25000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>20400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>32700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>50400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>27600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>51800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>22700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>17800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>17900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,558 +1947,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>2100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1500</v>
       </c>
       <c r="AG20" s="3">
         <v>1500</v>
       </c>
       <c r="AH20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E21" s="3">
         <v>92100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>86200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>97400</v>
       </c>
-      <c r="G21" s="3">
-        <v>104900</v>
-      </c>
       <c r="H21" s="3">
+        <v>91700</v>
+      </c>
+      <c r="I21" s="3">
         <v>81100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>77400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>74600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>68200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-10500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>23900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>33600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>43600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>47400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>33300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>32300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>45700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>37100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>37300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>48600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>32000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>27400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>8600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>37400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>23800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>21100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E22" s="3">
         <v>12300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>5400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>5300</v>
       </c>
       <c r="AB22" s="3">
         <v>5300</v>
       </c>
       <c r="AC22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AD22" s="3">
         <v>6200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>3700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>69900</v>
+      </c>
+      <c r="E23" s="3">
         <v>57900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>77900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>66000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>60400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>41700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>46100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>28300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>29900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>18700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>18200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>28700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>30500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>23500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>34500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>16500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>26800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>13500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>12600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>21400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,228 +2623,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E26" s="3">
         <v>51700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>56500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>50900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>45200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>49200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>38300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>39100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>13000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>17600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>33500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>22700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>28500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>21200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>39100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>13900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>71800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>22000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>10300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>9600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E27" s="3">
         <v>51200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>57100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>50200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>44200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>49000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>17600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>33500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>22700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>34100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>21200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>19400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>39100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>13900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>71800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>22000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>10300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>9600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,118 +2962,124 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-56100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>3700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-2500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-9400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-6100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-11600</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>316400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>91000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>11600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-7100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>7200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>11900</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>300</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>100</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>4400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>7100</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,228 +3301,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>11100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AG32" s="3">
         <v>-1500</v>
       </c>
       <c r="AH32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E33" s="3">
         <v>51200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>57100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>50200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>44200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>49000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-20400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>330300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>108700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>34600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>22800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>27100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>22700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>31000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>21500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>19200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>39200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>6600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>23000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>58600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>22300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>17400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,233 +3640,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E35" s="3">
         <v>51200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>57100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>50200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>44200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>49000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-20400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>330300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>108700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>34600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>22800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>27100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>22700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>31000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>21500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>19200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>39200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>6600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>23000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>58600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>22300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>17400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,151 +3955,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E41" s="3">
         <v>177800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>156900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>128100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>99400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>204800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>147800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>183400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>189800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>262800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>388200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>560100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>69100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>106900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>64000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>70700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>190200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>163100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>54700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>49300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>34600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>39000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>68800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>61900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>66700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>103700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>124300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>87200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>83500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>92700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>99600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E42" s="3">
         <v>2200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4089,459 +4179,474 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>405800</v>
+      </c>
+      <c r="E43" s="3">
         <v>357100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>324900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>376100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>357900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>349600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>296400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>338100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>318000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>307100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>294300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>296300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>274400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>253400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>261000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>238400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>267600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>342700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>270600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>327200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>329900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>335900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>352300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>333300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>332100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>338100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>360300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>346400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>339500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>313000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>267500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>266600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>252000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>232700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>251700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>321900</v>
+      </c>
+      <c r="E44" s="3">
         <v>308100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>271000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>297700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>292700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>295100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>276700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>291500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>299600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>265700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>244000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>265200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>235800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>220700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>189800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>170300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>157700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>169700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>143100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>179300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>181600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>175100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>154900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>157700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>155500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>151500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>128800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>143500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>141900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>109300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>143000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>165600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>168300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>159200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>145700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E45" s="3">
         <v>61600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>35000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>92800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>78600</v>
       </c>
       <c r="P45" s="3">
         <v>78600</v>
       </c>
       <c r="Q45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="R45" s="3">
         <v>64400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>77700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>407000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>76200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>185500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>67300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>69900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>70200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>22800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>23300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>25100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>40500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>71300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>74300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>72500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>97700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>39600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>35100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>26500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>30600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>920600</v>
+      </c>
+      <c r="E46" s="3">
         <v>906800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>784300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>827600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>808700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>779600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>709600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>768600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>739000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>819800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>721100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>837700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>778600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>815500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>903400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1046500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>901400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>695500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>675100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>648600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>769000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>744000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>632100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>563100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>545500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>553700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>598400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>623100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>622400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>598500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>632500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>559000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>538900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>511100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>527600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>700</v>
-      </c>
-      <c r="E47" s="3">
-        <v>700</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -4552,18 +4657,18 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3100</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4639,228 +4744,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E48" s="3">
         <v>223600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>275900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>275100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>270900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>217200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>182900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>135100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>134700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>110300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>156200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>107000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>110700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>155000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>108000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>113000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>186600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>147300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>187600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>178100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>176900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>209800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>202000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>199900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>204600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>184200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>185000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>188200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>185800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>186600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>188800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>191600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>193600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>195500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1955600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1803900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1537500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1585000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1587700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1605100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1385600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1362800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1385500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>854200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>856900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>852300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>875800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>896500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>872800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>741200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>735000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>800500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>673600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>792800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>697500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>694200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>701000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>660300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>660600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>661900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>592800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>594100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>595200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>478100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>463500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>463100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>462500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>459900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>458300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,118 +5196,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>199900</v>
+        <v>200800</v>
       </c>
       <c r="E52" s="3">
+        <v>200600</v>
+      </c>
+      <c r="F52" s="3">
         <v>111100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>116000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>112300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>193700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>157600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>202100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>236000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>231400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>196700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>685500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>725600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>744500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>697400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>594100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>661100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>614400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1447500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>621000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>611800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>606800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>591600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>637000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>661300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>681200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>682100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>704200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>718000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>749700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>757800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>721900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>736400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>733800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>731100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3306700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3137500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2714500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2806000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2783100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2799600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2439700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2473000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2501600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2021400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1930900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2482500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2489600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2567200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2628600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2489800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2410500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2297000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2333700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2250000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2256400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2221900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2134500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2062400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2067300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2101400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E57" s="3">
         <v>149000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>128100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>128200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>151400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>118700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>131700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>131000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>120000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>125200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>116200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>111000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>119600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>112300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>86800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>135000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>102100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>134500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>137900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>148000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>141600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>132500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>135900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>142200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>153600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>141200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>150700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>145000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>159700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>143300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>140800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>133100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>137600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E58" s="3">
         <v>88300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>48800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>290600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>337800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>144100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>142500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>72400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>13700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>178700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>108900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>121800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>113600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>270900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>262900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>143600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>59100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>73600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>89200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>49900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>122400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>133300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>57000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>52000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>35100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>32700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E59" s="3">
         <v>108000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>81900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>88200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>95200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>92000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>87500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>205500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>246900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>236900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>267900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>304700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>351500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>442100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>342900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>361600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>314100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>295200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>291200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>323400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>275200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>257100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>263600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>266700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>263400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>259900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>271500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>293800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>285700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>292500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>282700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>306000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>468000</v>
+      </c>
+      <c r="E60" s="3">
         <v>482900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>418300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>446300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>633300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>694800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>401200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>493700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>489600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>393900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>333800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>374400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>368200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>393900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>439500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>477500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>707600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>586800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>572100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>562200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>704000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>702100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>608600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>466800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>466600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>495000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>470200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>527000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>543900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>428200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>461000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>486000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>485300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>450900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>476300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>950300</v>
+      </c>
+      <c r="E61" s="3">
         <v>872000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>621500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>703900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>549300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>516600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>551600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>529800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>533100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>241500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>243000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>244600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>224500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>227700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>230800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>233900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>238000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>282600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>304000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>350300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>247000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>248600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>249900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>323800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>328000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>332300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>340600</v>
       </c>
       <c r="AE61" s="3">
         <v>340600</v>
       </c>
       <c r="AF61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AG61" s="3">
         <v>344900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>349300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>311000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>315400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>319400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>323500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E62" s="3">
         <v>236700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>94300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>186000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>210100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>237100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>113900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>235700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>225000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>274900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>783800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>808300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>829800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>855400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>718100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>736700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>766800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>817500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>754400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>753300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>756100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>773600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>810500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>836000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>858800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>840500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>869100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>880700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>905800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>915400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>880800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>920000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>917100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>921100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1773400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1694100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1330100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1447800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1499300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1562100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1245100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1326100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1329000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>895300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>851700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1402800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1401000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1451400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1525700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1429500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1682300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1636200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1693600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1666900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1704300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1706800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1632100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1601100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1630600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1686100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>342200</v>
+      </c>
+      <c r="E72" s="3">
         <v>290000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>238800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>181700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>131500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>87300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>38300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-51600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-24300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-51800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-68700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-399800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-461300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-477200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-512700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-535500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-562600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-584800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-610200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-631700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-650900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1533300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1443400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1384400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1358200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1283800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1237500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1194600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1146900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1172600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1126100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1079200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1079700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1088600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1115800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1102900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1060300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>728200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>660800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>640100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>583100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>552100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>515100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>502400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>461300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>436700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>415300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>414900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>369700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>358600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>333200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>314700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>255000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>208700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>211000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>191600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,233 +7918,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E81" s="3">
         <v>51200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>57100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>50200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>44200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>49000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-20400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>330300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>108700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>34600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>22800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>27100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>22700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>31000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>21500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>19200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>39200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>6600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>23000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>58600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>22300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>17400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,100 +8192,101 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E83" s="3">
         <v>6200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>14000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>9800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>8500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8100</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>7900</v>
       </c>
       <c r="AD83" s="3">
         <v>7900</v>
       </c>
       <c r="AE83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AF83" s="3">
         <v>6800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>6300</v>
       </c>
       <c r="AH83" s="3">
         <v>6300</v>
@@ -8099,13 +8298,16 @@
         <v>6300</v>
       </c>
       <c r="AK83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AL83" s="3">
         <v>4800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,118 +8868,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-10900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>166500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>51400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>126500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>72000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-26300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-14000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-39300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-57200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>20800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>74900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>60200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>69900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>78800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>43300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>97300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>8600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>56100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>52100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,118 +9024,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-2100</v>
       </c>
       <c r="Q91" s="3">
         <v>-2100</v>
       </c>
       <c r="R91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,118 +9361,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-306600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>32400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-303900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-550900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-184500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>582000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-84300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-24300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-93500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-67000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-74700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,8 +9517,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,8 +9550,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9394,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,334 +9967,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E100" s="3">
         <v>335700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-123800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-53600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-62200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>292700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-115500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>363300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>62900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>6200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-167700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>26500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-48600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-55300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>113000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>32700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>117500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>12900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-900</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E102" s="3">
         <v>20800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>27500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-117100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>55600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-30200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-74300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-126500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-164100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>491000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-37800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-119500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>108400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>14700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>37100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>16200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>637300</v>
+      </c>
+      <c r="E8" s="3">
         <v>592800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>552400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>482600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>533700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>483700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>501300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>465200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>469400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>448700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>423300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>399800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>429300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>370500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>354000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>307100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>349100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>285700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>296600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>287200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>345000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>268300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>258000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>369300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>444600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>364800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>372400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>343600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>445000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>362500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>379200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>351900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>387000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>348500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>349700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>340600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>284900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>383800</v>
+      </c>
+      <c r="E9" s="3">
         <v>352700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>323000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>286400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>315600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>286100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>299600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>281400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>277600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>258600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>249300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>267100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>237400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>229400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>203100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>217300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>189900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>194300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>182800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>219200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>176600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>169700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>255200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>301100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>258600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>264200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>260400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>309800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>274800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>281500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>261800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>306100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>263400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>273600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>252500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>177700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E10" s="3">
         <v>240100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>229400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>196200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>218100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>197600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>201700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>183800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>187900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>171100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>164700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>150500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>162200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>133100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>124600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>104000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>131800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>95800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>102300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>104400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>125800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>91700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>88300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>114100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>143500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>106200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>108200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>83200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>135200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>87700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>97700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>90100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>80900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>85100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>76100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>88100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>107200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,13 +1217,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>54700</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1219,11 +1232,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>46300</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1231,11 +1244,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>43300</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1321,8 +1334,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1437,240 +1453,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="E14" s="3">
         <v>9600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-18100</v>
-      </c>
       <c r="H14" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I14" s="3">
         <v>1600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>4800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>24200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>500</v>
       </c>
       <c r="AL14" s="3">
         <v>500</v>
       </c>
       <c r="AM14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AN14" s="3">
         <v>27600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>24600</v>
+        <v>18500</v>
       </c>
       <c r="E15" s="3">
         <v>24600</v>
       </c>
       <c r="F15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="G15" s="3">
         <v>19700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>16300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>11500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>14600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>6700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>6500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>5700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>1600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>100</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>200</v>
       </c>
       <c r="AM15" s="3">
         <v>200</v>
       </c>
       <c r="AN15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1708,240 +1733,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>564100</v>
+      </c>
+      <c r="E17" s="3">
         <v>488200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>458200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>410200</v>
       </c>
-      <c r="G17" s="3">
-        <v>461700</v>
-      </c>
       <c r="H17" s="3">
+        <v>449100</v>
+      </c>
+      <c r="I17" s="3">
         <v>403600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>425100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>399500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>402700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>388700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>366800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>349600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>454200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>334300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>326800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>295700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>320100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>268000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>279500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>262200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>302100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>247900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>240500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>336600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>394200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>337200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>346100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>340600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>393200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>349100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>356500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>332600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>386200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>317300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>345600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>322800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>267000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E18" s="3">
         <v>104600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>94200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>72400</v>
       </c>
-      <c r="G18" s="3">
-        <v>72000</v>
-      </c>
       <c r="H18" s="3">
+        <v>84600</v>
+      </c>
+      <c r="I18" s="3">
         <v>80100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>76200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>60000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>56500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>25000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>32700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>50400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>27600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>51800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>13400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>22700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>19300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>31200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>17800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>17900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1982,588 +2014,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>2100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-11100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1500</v>
       </c>
       <c r="AI20" s="3">
         <v>1500</v>
       </c>
       <c r="AJ20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E21" s="3">
         <v>126200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>117300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>92100</v>
       </c>
-      <c r="G21" s="3">
-        <v>86200</v>
-      </c>
       <c r="H21" s="3">
+        <v>98800</v>
+      </c>
+      <c r="I21" s="3">
         <v>95700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>77400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>74600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>68200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-10500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>23900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>32500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>47400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>33300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>32300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>42600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>45700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>37100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>48600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>32000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>27400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>37400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>8600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>23800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>21100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E22" s="3">
         <v>11600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>5300</v>
       </c>
       <c r="AD22" s="3">
         <v>5300</v>
       </c>
       <c r="AE22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AF22" s="3">
         <v>6200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>4000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>3700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E23" s="3">
         <v>81500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>69900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>57900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>77900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>66000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>60400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>51100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>41700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>46100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>23500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>29900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>18700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>28700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>30500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>23500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>34500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>16500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>26800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>13500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>12600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E24" s="3">
         <v>18400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>17400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>12400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>3000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2678,240 +2726,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E26" s="3">
         <v>63100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>52500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>56500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>50900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>45200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>49200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>38300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>39100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>17600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>13900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>17700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>22700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>28500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>39100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>13900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>71800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>22000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>10300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>9600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E27" s="3">
         <v>62700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>52200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>57100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>44200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>49000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>36000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>42800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>17600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>13900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>17700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>22700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>34100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>39100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>13900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>71800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>22000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>10300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>9600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3026,124 +3083,130 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-500</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>600</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-700</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-200</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-56100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-2300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>3700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-2500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-6100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1600</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-11600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>316400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>91000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>11600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-7100</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>7200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>11900</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>300</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>4400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>300</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>7100</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3258,8 +3321,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3374,240 +3440,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>23600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>14500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>11100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AI32" s="3">
         <v>-1500</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E33" s="3">
         <v>62700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>52200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>57100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>44200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>49000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-20400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>36000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>42800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-27300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>330300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>108700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>34600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>22800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>27100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>31000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>21500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>39200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>22300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>17400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3722,245 +3797,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E35" s="3">
         <v>62700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>52200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>57100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>44200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>49000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-20400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>36000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>42800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-27300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>330300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>108700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>34600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>22800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>27100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>31000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>21500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>39200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>22300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>17400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4001,8 +4085,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4043,163 +4128,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>364000</v>
+      </c>
+      <c r="E41" s="3">
         <v>229400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>156900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>124800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>128100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>99400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>87100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>204800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>147800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>183400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>189800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>262800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>388200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>560100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>69100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>106900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>64000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>70700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>190200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>163100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>54700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>49300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>34600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>39000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>68800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>61900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>66700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>103700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>124300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>87200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>83500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>92700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>99600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>2700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2200</v>
       </c>
-      <c r="G42" s="3">
-        <v>2700</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9100</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4275,489 +4364,504 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>422200</v>
+      </c>
+      <c r="E43" s="3">
         <v>456300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>405800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>357100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>324900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>376100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>357900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>349600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>296400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>338100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>318000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>307100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>294300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>296300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>274400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>253400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>261000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>238400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>267600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>342700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>270600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>327200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>329900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>335900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>352300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>333300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>332100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>338100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>360300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>346400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>339500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>313000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>267500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>266600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>252000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>232700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>251700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E44" s="3">
         <v>331300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>321900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>308100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>271000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>297700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>292700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>295100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>276700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>291500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>299600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>265700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>244000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>265200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>235800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>220700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>189800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>170300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>157700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>169700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>143100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>179300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>181600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>175100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>154900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>157700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>155500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>151500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>128800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>143500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>141900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>109300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>143000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>165600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>168300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>159200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>145700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E45" s="3">
         <v>44700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>58600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61600</v>
       </c>
-      <c r="G45" s="3">
-        <v>28800</v>
-      </c>
       <c r="H45" s="3">
+        <v>31500</v>
+      </c>
+      <c r="I45" s="3">
         <v>26900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>28500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>25300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>35000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>92800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>78600</v>
       </c>
       <c r="R45" s="3">
         <v>78600</v>
       </c>
       <c r="S45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="T45" s="3">
         <v>64400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>407000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>76200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>185500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>71400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>67300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>69900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>70200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>22800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>23300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>40500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>71300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>74300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>72500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>97700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>39600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>35100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>26500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>30600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1143700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1064400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>920600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>906800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>784300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>827600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>808700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>779600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>709600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>768600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>739000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>819800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>721100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>837700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>778600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>815500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>903400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1046500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>901400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>695500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>675100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>648600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>769000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>744000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>632100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>563100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>545500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>553700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>598400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>623100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>622400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>598500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>632500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>559000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>538900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>511100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>527600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>700</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
@@ -4768,18 +4872,18 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>1200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3100</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4855,240 +4959,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>367600</v>
+      </c>
+      <c r="E48" s="3">
         <v>227400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>226900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>223600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>275900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>275100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>270900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>217200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>182900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>135100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>134700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>110300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>156200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>109600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>110700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>155000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>108000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>113000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>186600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>147300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>187600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>178100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>176900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>209800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>202000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>199900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>204600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>184200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>185000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>188200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>185800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>186600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>188800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>191600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>193600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>195500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1911600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1924300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1955600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1803900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1537500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1585000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1587700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1605100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1385600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1362800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1385500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>854200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>856900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>852300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>875800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>896500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>872800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>741200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>735000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>800500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>673600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>792800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>697500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>694200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>701000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>660300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>660600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>661900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>592800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>594100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>595200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>478100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>463500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>463100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>462500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>459900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>458300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5203,8 +5316,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5319,124 +5435,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>179500</v>
+      </c>
+      <c r="E52" s="3">
         <v>226300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200600</v>
       </c>
-      <c r="G52" s="3">
-        <v>111100</v>
-      </c>
       <c r="H52" s="3">
+        <v>113700</v>
+      </c>
+      <c r="I52" s="3">
         <v>116000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>193700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>157600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>202100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>236000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>231400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>196700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>685500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>725600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>744500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>697400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>594100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>661100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>614400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1447500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>621000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>611800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>606800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>591600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>637000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>661300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>681200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>682100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>704200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>718000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>749700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>757800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>721900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>736400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>733800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>731100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5551,124 +5673,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3604600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3445600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3306700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3137500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2714500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2806000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2783100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2799600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2439700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2473000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2501600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2021400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1930900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2482500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2489600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2567200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2628600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2489800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2410500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2297000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2333700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2250000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2256400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2221900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2134500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2062400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2067300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2101400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5709,8 +5837,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5751,704 +5880,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E57" s="3">
         <v>157600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>140300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>149000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>128100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>128200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>151400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>118700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>131700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>131000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>120000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>124500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>125200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>116200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>111000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>119600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>112300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>86800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>135000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>102100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>134500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>137900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>148000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>141600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>132500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>135900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>142200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>153600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>141200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>150700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>145000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>159700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>143300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>140800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>133100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>137600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>69000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>48800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>290600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>337800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>144100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>142500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>72400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>15000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>178700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>108900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>121800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>113600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>270900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>262900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>143600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>59100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>73600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>89200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>49900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>122400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>133300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>11700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>57000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>52000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>35100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>32700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E59" s="3">
         <v>105000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>100000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>108000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>100600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>82100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>88200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>95200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>92000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>87500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>205500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>246900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>236900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>267900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>304700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>351500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>442100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>342900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>361600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>314100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>295200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>291200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>323400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>275200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>257100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>263600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>266700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>263400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>259900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>271500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>293800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>285700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>292500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>282700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>306000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>461100</v>
+      </c>
+      <c r="E60" s="3">
         <v>430900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>468000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>482900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>418300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>446300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>633300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>694800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>401200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>493700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>489600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>393900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>333800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>374400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>368200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>393900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>439500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>477500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>707600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>586800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>572100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>562200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>704000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>702100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>608600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>466800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>466600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>495000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>470200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>527000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>543900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>428200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>461000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>486000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>485300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>450900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>476300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>558100</v>
+      </c>
+      <c r="E61" s="3">
         <v>499800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>950300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>872000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>621500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>703900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>549300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>516600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>551600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>529800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>533100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>241500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>243000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>244600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>224500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>227700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>230800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>233900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>238000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>282600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>304000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>350300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>247000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>248600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>249900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>323800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>328000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>332300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>340600</v>
       </c>
       <c r="AG61" s="3">
         <v>340600</v>
       </c>
       <c r="AH61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AI61" s="3">
         <v>344900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>349300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>311000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>315400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>319400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>323500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>102100</v>
+      </c>
+      <c r="E62" s="3">
         <v>228800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>232900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>236700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>94300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>186000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>210100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>237100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>113900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>235700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>226500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>225000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>274900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>783800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>808300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>829800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>855400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>718100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>736700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>766800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>817500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>754400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>753300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>756100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>773600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>810500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>836000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>858800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>840500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>869100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>880700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>905800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>915400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>880800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>920000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>917100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>921100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6563,8 +6711,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6679,8 +6830,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6795,124 +6949,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1367100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1297300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1773400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1694100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1330100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1447800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1499300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1562100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1245100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1326100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1329000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>895300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>851700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1402800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1401000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1451400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1525700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1429500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1682300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1636200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1693600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1666900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1704300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1706800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1632100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1601100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1630600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1686100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6953,8 +7113,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7069,8 +7230,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7185,8 +7349,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7301,8 +7468,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7417,124 +7587,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>482800</v>
+      </c>
+      <c r="E72" s="3">
         <v>404900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>342200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>290000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>238800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>181700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>131500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>87300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>38300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-40400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-51800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-68700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-399800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-461300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-477200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-512700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-535500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-562600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-584800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-610200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-631700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-650900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7649,8 +7825,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7765,8 +7944,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7881,124 +8063,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2237500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2148300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1533300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1443400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1384400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1358200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1283800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1237500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1194600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1146900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1172600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1126100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1079200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1079700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1088600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1115800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1102900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1060300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>728200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>660800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>640100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>583100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>552100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>515100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>502400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>461300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>436700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>415300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>414900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>369700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>358600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>333200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>314700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>255000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>208700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>211000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>191600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8113,245 +8301,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>77900</v>
+      </c>
+      <c r="E81" s="3">
         <v>62700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>52200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>57100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>44200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>49000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-20400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>36000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>42800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-27300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>330300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>108700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>34600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>22800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>27100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>31000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>21500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>39200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>22300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>17400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8392,106 +8589,107 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>14000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>11100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>9300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>8100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8100</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>7900</v>
       </c>
       <c r="AF83" s="3">
         <v>7900</v>
       </c>
       <c r="AG83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AH83" s="3">
         <v>6800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>6300</v>
       </c>
       <c r="AJ83" s="3">
         <v>6300</v>
@@ -8503,13 +8701,16 @@
         <v>6300</v>
       </c>
       <c r="AM83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AN83" s="3">
         <v>4800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8624,8 +8825,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8740,8 +8944,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8856,8 +9063,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8972,8 +9182,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9088,124 +9301,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E89" s="3">
         <v>106500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>166500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>51400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>57500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>10500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>126500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>72000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-39300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-57200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>74900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>60200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>69900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>26700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>78800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>43300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>97300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>8600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>56100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>52100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9246,124 +9465,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-2100</v>
       </c>
       <c r="S91" s="3">
         <v>-2100</v>
       </c>
       <c r="T91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9478,8 +9701,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9594,124 +9820,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-41400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-151200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-306600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>32400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-303900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-550900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-57800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-184500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>582000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-84300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-93500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-74700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9752,8 +9984,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9790,8 +10023,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9868,8 +10101,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9984,8 +10220,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10100,8 +10339,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10216,352 +10458,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3">
         <v>29300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>59600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>335700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-123800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-53600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-62200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>292700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-115500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>363300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>62900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-35000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-167700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>26500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-48600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>113000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-18400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>32700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>117500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>1200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>12900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>4400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-900</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E102" s="3">
         <v>94500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>20800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>32000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-117100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>55600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-74300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-126500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-164100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>491000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-37800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-119500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>108400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>14700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>37100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>16200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-18600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPXC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>SPXC</t>
   </si>
@@ -656,527 +656,540 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>566800</v>
+      </c>
+      <c r="E8" s="3">
         <v>637300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>592800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>552400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>482600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>533700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>483700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>501300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>465200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>469400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>448700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>423300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>399800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>429300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>370500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>354000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>307100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>349100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>285700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>296600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>287200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>345000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>268300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>258000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>369300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>444600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>364800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>372400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>343600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>445000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>362500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>379200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>351900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>387000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>348500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>349700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>340600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>284900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>345000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>335700</v>
+      </c>
+      <c r="E9" s="3">
         <v>383800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>352700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>323000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>286400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>315600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>286100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>299600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>281400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>281500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>277600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>258600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>249300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>267100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>237400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>229400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>203100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>217300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>189900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>194300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>182800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>219200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>176600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>169700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>255200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>301100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>258600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>264200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>260400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>309800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>274800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>281500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>261800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>306100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>263400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>273600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>252500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>177700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>264200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>231100</v>
+      </c>
+      <c r="E10" s="3">
         <v>253500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>240100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>229400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>196200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>218100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>197600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>201700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>183800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>187900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>171100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>164700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>150500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>162200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>133100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>124600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>104000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>131800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>95800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>102300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>104400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>125800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>91700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>88300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>114100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>143500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>106200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>108200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>83200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>135200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>87700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>97700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>90100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>80900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>85100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>76100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>88100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>107200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>80800</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1218,16 +1231,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>54700</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1235,11 +1249,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>46300</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1247,11 +1261,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>43300</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1337,8 +1351,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1456,246 +1473,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-39800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>9600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8200</v>
       </c>
-      <c r="G14" s="3">
-        <v>3100</v>
-      </c>
       <c r="H14" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-5500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>4800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>24200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-9200</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>500</v>
       </c>
       <c r="AM14" s="3">
         <v>500</v>
       </c>
       <c r="AN14" s="3">
+        <v>500</v>
+      </c>
+      <c r="AO14" s="3">
         <v>27600</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E15" s="3">
         <v>18500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>24600</v>
       </c>
       <c r="F15" s="3">
         <v>24600</v>
       </c>
       <c r="G15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H15" s="3">
         <v>19700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>16300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>16600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>9300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>5500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>6500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>5700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>3300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>1600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>1500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>1700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>100</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>200</v>
       </c>
       <c r="AN15" s="3">
         <v>200</v>
       </c>
       <c r="AO15" s="3">
+        <v>200</v>
+      </c>
+      <c r="AP15" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1734,246 +1760,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>472500</v>
+      </c>
+      <c r="E17" s="3">
         <v>564100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>488200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>458200</v>
       </c>
-      <c r="G17" s="3">
-        <v>410200</v>
-      </c>
       <c r="H17" s="3">
+        <v>409100</v>
+      </c>
+      <c r="I17" s="3">
         <v>449100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>403600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>425100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>399500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>402700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>388700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>366800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>349600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>454200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>334300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>326800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>295700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>320100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>268000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>279500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>262200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>302100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>247900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>240500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>336600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>394200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>337200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>346100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>340600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>393200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>349100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>356500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>332600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>386200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>317300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>345600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>322800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>267000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>335000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>94300</v>
+      </c>
+      <c r="E18" s="3">
         <v>73200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>94200</v>
       </c>
-      <c r="G18" s="3">
-        <v>72400</v>
-      </c>
       <c r="H18" s="3">
+        <v>73500</v>
+      </c>
+      <c r="I18" s="3">
         <v>84600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>80100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>76200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>60000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>56500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>50200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>29000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>25000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>17500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>32700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>50400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>51800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>22700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>19300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>31200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>17800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>17900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2015,603 +2048,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>4900</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T20" s="3">
+        <v>6600</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="V20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="W20" s="3">
+        <v>6400</v>
+      </c>
+      <c r="X20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="E20" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="AE20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="AH20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>900</v>
-      </c>
-      <c r="P20" s="3">
-        <v>4900</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-23600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>6600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-8100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>3900</v>
-      </c>
-      <c r="V20" s="3">
-        <v>6400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>7500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>5500</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-14500</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AI20" s="3">
         <v>2500</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>7500</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-11100</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1500</v>
       </c>
       <c r="AJ20" s="3">
         <v>1500</v>
       </c>
       <c r="AK20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>90300</v>
+        <v>115900</v>
       </c>
       <c r="E21" s="3">
+        <v>90700</v>
+      </c>
+      <c r="F21" s="3">
         <v>126200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>117300</v>
       </c>
-      <c r="G21" s="3">
-        <v>92100</v>
-      </c>
       <c r="H21" s="3">
+        <v>93200</v>
+      </c>
+      <c r="I21" s="3">
         <v>98800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>95700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>81100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>77400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>74600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>68200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>23900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>33600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>32500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>47400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>33300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>32300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>42600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>45700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>37300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>48600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>32000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>27400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>8600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>37400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>8600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>23800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>21100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>18400</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>8600</v>
+        <v>8400</v>
       </c>
       <c r="E22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F22" s="3">
         <v>11600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>2200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>4800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>4700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>5300</v>
       </c>
       <c r="AE22" s="3">
         <v>5300</v>
       </c>
       <c r="AF22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AG22" s="3">
         <v>6200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>4600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>4000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>3700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E23" s="3">
         <v>104800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>81500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>69900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>57900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>77900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>66000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>60400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>41700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>48100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>46100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>50400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>23500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>20100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>29900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>18700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>18200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>28700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>34500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>20100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>16500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>26800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-2300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>13500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>12600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="3">
         <v>26600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>12400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-4600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-73700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>6000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>3200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>3000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2729,246 +2778,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E26" s="3">
         <v>78200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>52500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>51700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>56500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>45200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>35700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>38300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>39100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>17600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>13900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>17700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>15200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>22700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>28500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>39100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>71800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>22000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-8300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>10300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>9600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E27" s="3">
         <v>77900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>52200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>57100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>44200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-20400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>36000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>42800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>17600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>13900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>17700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>33500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>15200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>22700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>34100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>39100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>71800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>22000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-8300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>10300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>9600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3086,127 +3144,133 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-200</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-56100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-2300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>3700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-9400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-6100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-11600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>316400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>91000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>11600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>7200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>11900</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>300</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>4400</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-13200</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>300</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-700</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>7100</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-95700</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3324,8 +3388,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3443,246 +3510,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="L32" s="3">
+        <v>600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="R32" s="3">
+        <v>23600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="U32" s="3">
+        <v>8100</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="E32" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="AE32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>11100</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-900</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>23600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>8100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-6400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>8600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>14500</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AI32" s="3">
         <v>-2500</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>-7500</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>11100</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1500</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1500</v>
       </c>
       <c r="AK32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E33" s="3">
         <v>77900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>62700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>52200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>57100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>44200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>49000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-20400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>36000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>42800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>330300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>108700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>34600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>22800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>27100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>22700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>31000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>21500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>39200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>58600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>22300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>17400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-86100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3800,251 +3876,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E35" s="3">
         <v>77900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>62700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>52200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>57100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>44200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>49000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-20400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>36000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>42800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>330300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>108700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>34600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>22800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>27100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>22700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>31000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>21500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>39200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>58600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>22300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>17400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-86100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4086,8 +4171,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4129,127 +4215,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E41" s="3">
         <v>364000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>229400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>177800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>156900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>124800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>128100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>99400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>87100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>204800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>147800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>183400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>189800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>262800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>388200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>560100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>69100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>106900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>64000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>70700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>190200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>163100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>54700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>49300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>34600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>39000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>68800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>61900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>66700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>103700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>124300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>87200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>83500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>92700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>99600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>83400</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4257,41 +4347,41 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>9100</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4367,504 +4457,519 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>470400</v>
+      </c>
+      <c r="E43" s="3">
         <v>422200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>456300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>405800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>357100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>324900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>376100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>357900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>349600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>296400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>338100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>318000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>307100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>294300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>296300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>274400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>253400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>261000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>238400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>267600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>342700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>270600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>327200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>329900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>335900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>352300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>333300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>332100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>338100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>360300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>346400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>339500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>313000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>267500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>266600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>252000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>232700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>251700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>318000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>342400</v>
+      </c>
+      <c r="E44" s="3">
         <v>302200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>331300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>321900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>308100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>271000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>297700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>292700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>295100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>276700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>291500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>299600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>265700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>244000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>265200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>235800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>220700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>189800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>170300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>157700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>169700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>143100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>179300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>181600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>175100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>154900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>157700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>155500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>151500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>128800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>143500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>141900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>109300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>143000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>165600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>168300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>159200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>145700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>176700</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E45" s="3">
         <v>55300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>58600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>61600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>31500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>28500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>35000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>92800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>78600</v>
       </c>
       <c r="S45" s="3">
         <v>78600</v>
       </c>
       <c r="T45" s="3">
+        <v>78600</v>
+      </c>
+      <c r="U45" s="3">
         <v>64400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>77700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>407000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>76200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>185500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>71400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>67300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>69900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>70200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>22800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>23300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>25100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>40500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>71300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>74300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>72500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>97700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>39600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>35100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>26500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>30600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>50700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1013000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1143700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1064400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>920600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>906800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>784300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>827600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>808700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>779600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>709600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>768600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>739000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>819800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>721100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>837700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>778600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>815500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>903400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1046500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>901400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>695500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>675100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>648600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>769000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>744000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>632100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>563100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>545500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>553700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>598400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>623100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>622400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>598500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>632500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>559000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>538900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>511100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>527600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>628800</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="3">
+        <v>58200</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>300</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>700</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -4875,18 +4980,18 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>1200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3100</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4962,246 +5067,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>307200</v>
+      </c>
+      <c r="E48" s="3">
         <v>367600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>227400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>226900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>223600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>275900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>275100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>270900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>217200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>182900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>135100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>134700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>110300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>156200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>107000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>109600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>110700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>155000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>108000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>113000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>186600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>147300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>187600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>178100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>176900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>209800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>202000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>199900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>204600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>184200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>185000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>188200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>185800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>186600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>188800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>191600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>193600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>195500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2296500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1911600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1924300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1955600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1803900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1537500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1585000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1587700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1605100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1385600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1362800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1385500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>854200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>856900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>852300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>875800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>896500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>872800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>741200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>735000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>800500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>673600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>792800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>697500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>694200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>701000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>660300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>660600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>661900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>592800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>594100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>595200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>478100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>463500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>463100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>462500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>459900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>458300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>488800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5319,8 +5433,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5438,127 +5555,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>202500</v>
+      </c>
+      <c r="E52" s="3">
         <v>179500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>226300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>113700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>112300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>193700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>157600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>202100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>236000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>231400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>196700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>685500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>725600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>744500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>697400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>594100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>661100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>614400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1447500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>621000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>611800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>606800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>591600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>637000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>661300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>681200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>682100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>704200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>718000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>749700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>757800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>721900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>736400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>733800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>731100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>661800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5676,127 +5799,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3879500</v>
+      </c>
+      <c r="E54" s="3">
         <v>3604600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3445600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3306700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3137500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2714500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2806000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2783100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2799600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2439700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2473000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2501600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2021400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1930900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2482500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2489600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2567200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2628600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2489800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2410500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2297000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2333700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2250000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2256400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2221900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2134500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2062400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2067300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2101400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2057500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2106400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2123800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2012100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2040400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1932800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1929400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1898400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1912500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1989500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5838,8 +5967,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5881,722 +6011,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>164600</v>
+      </c>
+      <c r="E57" s="3">
         <v>145200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>157600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>140300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>149000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>128100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>128200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>151400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>118700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>131700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>131000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>120000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>124500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>125200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>116200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>111000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>119600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>112300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>86800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>135000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>102100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>134500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>137900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>148000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>141600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>132500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>135900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>142200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>153600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>141200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>150700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>145000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>159700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>143300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>140800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>133100</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>137600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E58" s="3">
         <v>19300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>82500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>290600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>337800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>144100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>142500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>72400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>15100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>15000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>15200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>13700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>178700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>108900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>121800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>113600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>270900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>262900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>143600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>59100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>73600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>89200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>49900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>122400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>133300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>57000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>52000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>35100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>32700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>32800</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E59" s="3">
         <v>146500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>105000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>100000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>108000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>81900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>82100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>88200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>95200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>92000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>87500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>205500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>246900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>236900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>267900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>304700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>351500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>442100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>342900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>361600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>314100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>295200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>291200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>323400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>275200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>257100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>263600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>266700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>263400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>259900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>271500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>293800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>285700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>292500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>282700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>306000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>358400</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>481200</v>
+      </c>
+      <c r="E60" s="3">
         <v>461100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>430900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>468000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>482900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>418300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>446300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>633300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>694800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>401200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>493700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>489600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>393900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>333800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>374400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>368200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>393900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>439500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>477500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>707600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>586800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>572100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>562200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>704000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>702100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>608600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>466800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>466600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>495000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>470200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>527000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>543900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>428200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>461000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>486000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>485300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>450900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>476300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>534500</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>643700</v>
+      </c>
+      <c r="E61" s="3">
         <v>558100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>499800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>950300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>872000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>621500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>703900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>549300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>516600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>551600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>529800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>533100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>241500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>243000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>244600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>224500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>227700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>230800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>233900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>238000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>282600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>304000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>350300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>247000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>248600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>249900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>323800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>328000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>332300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>331900</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>340600</v>
       </c>
       <c r="AH61" s="3">
         <v>340600</v>
       </c>
       <c r="AI61" s="3">
+        <v>340600</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>344900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>349300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>311000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>315400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>319400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>323500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>331200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>258100</v>
+      </c>
+      <c r="E62" s="3">
         <v>102100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>228800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>232900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>236700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>94300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>186000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>210100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>237100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>113900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>235700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>226500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>225000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>274900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>783800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>808300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>829800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>855400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>718100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>736700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>766800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>817500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>754400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>753300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>756100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>773600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>810500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>836000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>858800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>840500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>869100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>880700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>905800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>915400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>880800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>920000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>917100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>921100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>850400</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6714,8 +6863,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6833,8 +6985,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6952,127 +7107,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1594100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1367100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1297300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1773400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1694100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1330100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1447800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1499300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1562100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1245100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1326100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1329000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>895300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>851700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1402800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1401000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1451400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1525700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1429500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1682300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1636200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1693600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1666900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1704300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1706800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1632100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1601100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1630600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1686100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1642600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1736700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1765200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1678900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1725700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1677800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1720700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1687400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1720900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1716100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7114,8 +7275,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7233,8 +7395,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7352,8 +7517,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7471,8 +7639,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7590,127 +7761,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>542700</v>
+      </c>
+      <c r="E72" s="3">
         <v>482800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>404900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>342200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>290000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>238800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>181700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>131500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>87300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>38300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-24300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-40400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-51800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-68700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-399800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-461300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-477200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-512700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-535500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-562600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-584800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-610200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-631700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-650900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-650100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-701300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-707900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-730900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-742300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-800900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-823200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-814200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-831600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7828,8 +8005,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7947,8 +8127,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8066,127 +8249,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2285400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2237500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2148300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1533300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1443400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1384400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1358200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1283800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1237500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1194600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1146900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1172600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1126100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1079200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1079700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1088600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1115800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1102900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1060300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>728200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>660800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>640100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>583100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>552100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>515100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>502400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>461300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>436700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>415300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>414900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>369700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>358600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>333200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>314700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>255000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>208700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>211000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>191600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>273400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8304,251 +8493,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E81" s="3">
         <v>77900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>62700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>52200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>57100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>44200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>49000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-20400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>36000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>42800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>330300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>108700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>34600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>22800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>27100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>22700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>31000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>21500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>39200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>12400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>58600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>22300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>17400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-86100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8590,109 +8788,110 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>14000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>8100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>8500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>8100</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>7900</v>
       </c>
       <c r="AG83" s="3">
         <v>7900</v>
       </c>
       <c r="AH83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="AI83" s="3">
         <v>6800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>6600</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>6300</v>
       </c>
       <c r="AK83" s="3">
         <v>6300</v>
@@ -8704,13 +8903,16 @@
         <v>6300</v>
       </c>
       <c r="AN83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="AO83" s="3">
         <v>4800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>7500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8828,8 +9030,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8947,8 +9152,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9066,8 +9274,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9185,8 +9396,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9304,127 +9518,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E89" s="3">
         <v>195200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>106500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>42500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>166500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>51400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>57500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>10500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>126500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>72000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-14000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-39300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-57200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>20800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>74900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>60200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>69900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>30100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>26700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>78800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>43300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>15900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>97300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>8600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>56100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>6900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-17100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>52100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-6200</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9466,127 +9686,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3900</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-2100</v>
       </c>
       <c r="T91" s="3">
         <v>-2100</v>
       </c>
       <c r="U91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V91" s="3">
         <v>-3300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-4100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9704,8 +9928,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9823,127 +10050,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-395800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-41400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-151200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-306600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>32400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-303900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-550900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-57800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-184500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>582000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-84300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-93500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-67000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-74700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-156000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9985,8 +10218,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10026,8 +10260,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10104,8 +10338,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10223,8 +10460,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10342,8 +10582,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10461,361 +10704,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E100" s="3">
         <v>900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>29300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>59600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>335700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-123800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-53600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-62200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>292700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-115500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>363300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>62900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-35000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-167700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-48600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>113000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-18400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>32700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-86000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-11100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>117500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>1200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>12900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-7400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-10900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-3500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-900</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>3600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-207700</v>
+      </c>
+      <c r="E102" s="3">
         <v>134600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>94500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>32000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>27500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-117100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>55600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-74300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-126500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-164100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>491000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-37800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-119500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>108400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>14700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-29800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-37000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-20600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>37100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>3700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-6900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>16200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-18600</v>
       </c>
     </row>
